--- a/tools/samples/mentors.xlsx
+++ b/tools/samples/mentors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airah/Desktop/WCC/wcc/tools/samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFF700C-8ECE-4C43-A867-EA99E59234B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AFF2F1-1A47-2F47-9E1F-6C4FFD50AA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="553">
   <si>
     <t>What is your full name?</t>
   </si>
@@ -125,9 +125,6 @@
     <t xml:space="preserve">Mentor2 Name   </t>
   </si>
   <si>
-    <t>Mentor2</t>
-  </si>
-  <si>
     <t>Fullstack Developer</t>
   </si>
   <si>
@@ -156,9 +153,6 @@
   </si>
   <si>
     <t>Both</t>
-  </si>
-  <si>
-    <t>Mentor3</t>
   </si>
   <si>
     <t>4-5 Years</t>
@@ -249,19 +243,1687 @@
     <t>she/her</t>
   </si>
   <si>
-    <t>Frontend system</t>
-  </si>
-  <si>
-    <t>mentor1@gmail.com</t>
-  </si>
-  <si>
-    <t>Mentor2 Name</t>
-  </si>
-  <si>
-    <t>Mentor3 Name</t>
-  </si>
-  <si>
     <t>Ad-Hoc Format only</t>
+  </si>
+  <si>
+    <t>Rajani Rao</t>
+  </si>
+  <si>
+    <t>rajaniraog@gmail.com</t>
+  </si>
+  <si>
+    <t>Cambridge, UK</t>
+  </si>
+  <si>
+    <t>CTO/Principal Technologist</t>
+  </si>
+  <si>
+    <t>WInvest/AVEVA</t>
+  </si>
+  <si>
+    <t>16+ Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rajani Rao is a Principal Technologist at AVEVA, designing scalable, web and IoT solutions in the Cloud with over two decades of experience in computing. Outside of her profession, she is a mother of two girls and an advocate for women in tech. As a dynamic speaker and panelist, Rajani shares insights on technology, engineering, and female leadership. She holds an advisory role at Pixuate, a female-led AI and Machine Learning startup. Rajani extends her leadership as Director at WomenWhoCode London, fostering technical skill-building and career progression. She serves as a fractional CTO at WInvest, committed to an inclusive financial ecosystem using AI. Rajani's vision is to shape an inclusive, innovative global tech landscape.
+</t>
+  </si>
+  <si>
+    <t>Anything Software Engineering</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>Distributed Systems</t>
+  </si>
+  <si>
+    <t>DevOps</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>Grow beyond senior level</t>
+  </si>
+  <si>
+    <t>Grow from mid-level to senior-level</t>
+  </si>
+  <si>
+    <t>Switch from IC to management position</t>
+  </si>
+  <si>
+    <t>C#</t>
+  </si>
+  <si>
+    <t>C++</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Is really keen to grow</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rajaniraog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://calendly.com/rajaniraog/1-1 </t>
+  </si>
+  <si>
+    <t>Woman</t>
+  </si>
+  <si>
+    <t>Eleonora Belova</t>
+  </si>
+  <si>
+    <t>eleonora.belova.16@gmail.com</t>
+  </si>
+  <si>
+    <t>The Netherlands</t>
+  </si>
+  <si>
+    <t>Test Automation Engineer</t>
+  </si>
+  <si>
+    <t>IBM Security</t>
+  </si>
+  <si>
+    <t>2-4 Years</t>
+  </si>
+  <si>
+    <t>I am a dedicated Test Automation Engineer with a passion for ensuring software quality. To me, testing is way more than just identifying bugs and flaws; it’s about viewing processes and products through the lens of the end user. My expertise includes UI test automation, particularly with Playwright, and API test automation using tools like Postman and PactumJS. Beyond the technical part, I am interested in exploring different aspects in team communication, cross-cultural collaboration and contributing to professional communities through volunteering. I find immense joy in sharing my insights through articles and engaging in meaningful discussions with peers. Moreover, I am eager to help individuals start their journey in software testing. I can share industry knowledge, assist in reviewing your CV, and provide guidance on various related topics.</t>
+  </si>
+  <si>
+    <t>Test Automation, Quality Assurance, Starting career in IT, CV Review, Preparation for the Interview, Exploratory Testing, Web Testing (Manual &amp; Automation), API Testing (Postman, SOAP UI), Python for Software Testers, Career Advice, ISTQB Foundation Certification Preparation guidelines</t>
+  </si>
+  <si>
+    <t>Quality Assurance</t>
+  </si>
+  <si>
+    <t>JavaScript</t>
+  </si>
+  <si>
+    <t>Typescript</t>
+  </si>
+  <si>
+    <t>I would love to connect with an open-minded early-career engineer, who is interested in learning new things in Software Testing, or wants to know how to navigate in career. I can also help people who are switched from different fields to Software Testing and provide guidance and resources.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/eleonora-belova-7069baa5/</t>
+  </si>
+  <si>
+    <t>https://github.com/nora-weisser
+https://noraweisser.com/</t>
+  </si>
+  <si>
+    <t>Ken Pemberton</t>
+  </si>
+  <si>
+    <t>kenpem@gmail.com</t>
+  </si>
+  <si>
+    <t>Chesham, Buckinghamshire, UK</t>
+  </si>
+  <si>
+    <t>PEOPLE-FIRST servant-leadership of technical teams</t>
+  </si>
+  <si>
+    <t>To be determined!</t>
+  </si>
+  <si>
+    <t>I started coding as a teenager, and 40 years later it still fascinates me, although I've stepped away from programming now to focus on honing my management skills as a servant-leader.
+So while I won't be able to help you actually write code, I might be able to help guide you past the self-doubt that's inevitable as you step up to something new, be it a career or a promotion.</t>
+  </si>
+  <si>
+    <t>Overcoming self-doubt
+Dealing with change
+How to work effectively with others
+Relating to difficult colleagues
+Building resilience
+Interview preparation
+CV review</t>
+  </si>
+  <si>
+    <t>Engineering management</t>
+  </si>
+  <si>
+    <t>Folks who would benefit from coaching for confidence and resilience within the tech world. You are more capable than you know!</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kenpemberton</t>
+  </si>
+  <si>
+    <t>https://grumpyoldfart.org/</t>
+  </si>
+  <si>
+    <t>Prefer not to say</t>
+  </si>
+  <si>
+    <t>Irina Kamalova</t>
+  </si>
+  <si>
+    <t>iren.kamalova@gmail.com</t>
+  </si>
+  <si>
+    <t>@Irina Kamalova</t>
+  </si>
+  <si>
+    <t>London, UK</t>
+  </si>
+  <si>
+    <t>Backend Software Engineer</t>
+  </si>
+  <si>
+    <t>Revolut</t>
+  </si>
+  <si>
+    <t>Long-Term Format</t>
+  </si>
+  <si>
+    <t>English, Russian</t>
+  </si>
+  <si>
+    <t>5-7 Years</t>
+  </si>
+  <si>
+    <t>Irina is a backend SWE at Revolut and if the Director of WWCode London. Her job involved constantly completing the product development lifecycle of successfully launched applications and supporting requests from 20 million customers at Revolut.
+Her experience as a Software Engineer included working with large projects, search engines, distributed systems, performance issues, and huge data storage. Apart from being a strong developer and a good team player, in the last 2-years, she volunteered for CodeFirst: Girls and Women Who Code London and grew up from volunteer to lead and, in the end, to a Director of community. She organised a team to deliver outstanding projects and show impressive results. She built a guild of volunteers to deliver a Mentorship Programme, technical tracks, help with resumes, mock interviews and overall grown community more than twice.
+Currently, she’s working at Revolut and building a platform for retail products. That includes support services to handle our 20 million clients, handle huge throughput and provide law latency for data flow. Irina constantly helps her team to tackle the extra mile and help the company to improve an intervening process, onboarding new hires and running knowledge-sharing activities. As a cherry on top, she helped to launch the inner Revolut Women Guild “RevWomen”.</t>
+  </si>
+  <si>
+    <t>Software Development Strategies, Resume Review, Preparation for The Technical Interview, Pets Projects, Concurrency, Databases, System Design, Low level application design, TDD, DDD, Software Architecture, Distributive Systems, Integration with stack holders, CQRS, Deployment, Data Migration, Stability</t>
+  </si>
+  <si>
+    <t>Data Engineering</t>
+  </si>
+  <si>
+    <t>Kotlin</t>
+  </si>
+  <si>
+    <t>Scala</t>
+  </si>
+  <si>
+    <t>A mentee who wants to grow from Mid to Senior, or want to change their job and prepare for an interview for Mid/Senior position. Based in London, working in Fin tech, Backend Engineer</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/irina-kamalova/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/iren-kamalova/30min</t>
+  </si>
+  <si>
+    <t>Thank you for the awesome launch!</t>
+  </si>
+  <si>
+    <t>Ana Nogal</t>
+  </si>
+  <si>
+    <t>ana.nogal@gmail.com</t>
+  </si>
+  <si>
+    <t>Barcelona, Spain</t>
+  </si>
+  <si>
+    <t>Senior iOS Developer</t>
+  </si>
+  <si>
+    <t>Novoda</t>
+  </si>
+  <si>
+    <t>English, Spanish, Portuguese</t>
+  </si>
+  <si>
+    <t>I'm a senior iOS developer with ten years of business experience and over 25 years in software development. I spent the first 15 years working as a back-end developer in .NET and Java, but I fell in love when I discovered Mobile development. I am passionate about the quality and maintainability of the application's code and architecture. 
+I have already lived in some European cities, such as Lisbon, Madrid, Barcelona and London. This allowed me to work in different cultures and dynamics, further increasing my ability to connect, communicate and grow. I love giving back to the community, so I started collaborating with DevPass, helping guide newcomers. I'm also a mentor at MentoCruise, for those who want a more professional follow-up.</t>
+  </si>
+  <si>
+    <t>TDD
+Clean code
+Refactoring
+Team dynamics
+Mock interview
+PR reviews
+Code Principles</t>
+  </si>
+  <si>
+    <t>iOS</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>Swift</t>
+  </si>
+  <si>
+    <t>Well, I like to help essentially. I have had mentees that needed more a hands on, pair-programming with them, and others that orientation was enough. I'm ok with both scenarios.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ananogal/</t>
+  </si>
+  <si>
+    <t>https://www.ananogal.com/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/ana-nogal/women-community-session</t>
+  </si>
+  <si>
+    <t>I can be a little more flexible with the hours if that means that nobody stays without a mentor</t>
+  </si>
+  <si>
+    <t>Sonali Goel</t>
+  </si>
+  <si>
+    <t>goelsonali@gmail.com</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>Senior Developer</t>
+  </si>
+  <si>
+    <t>Yoox-Net-A-Porter</t>
+  </si>
+  <si>
+    <t>Ad-Hoc Format</t>
+  </si>
+  <si>
+    <t>10-15 Years</t>
+  </si>
+  <si>
+    <t>An accomplished technical lead with over a decade of experience in the technology field have successfully led global teams in various capacities. Worked as a consultant in the past and currently working as a senior SME for a luxury online fashion brand, have excelled in designing and implementing scalable applications. Always keen to learn something new and ready to take up challenges.</t>
+  </si>
+  <si>
+    <t>Software Development Processes and Overview, Guidance on how to prepare for Interviews, BDD and TDD approach to development. AWS solution guidance/path for study or certifications.</t>
+  </si>
+  <si>
+    <t>New to tech or someone who needs some guidance about tech world or someone needs to grow</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sonali-goel-6b611522/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/sonali_goel/mentorship</t>
+  </si>
+  <si>
+    <t>Adeola Adekoyejo</t>
+  </si>
+  <si>
+    <t>adekoyejoadeola@gmail.com</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Full stack Engineer</t>
+  </si>
+  <si>
+    <t>Nill</t>
+  </si>
+  <si>
+    <t>I am Frontend engineer with 4years of experience. I have had opportunities of working with several companies and building sustainable products for them. I am very keen to solving problems and helping people as well</t>
+  </si>
+  <si>
+    <t>Frontend interview prep, technical writing, system design, web accessibility, testing</t>
+  </si>
+  <si>
+    <t>You don’t have to know so much as long as you are willing to learn and do the work from your end</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/adeola-adekoyejo-405799115?trk=contact-info</t>
+  </si>
+  <si>
+    <t>https://medium.com/@adekoyejoadeola</t>
+  </si>
+  <si>
+    <t>https://calendly.com/adekoyejoadeola/60min</t>
+  </si>
+  <si>
+    <t>Can schedule a calendar based on on what works for me and my mentee</t>
+  </si>
+  <si>
+    <t>Sakirat Kehinde Usman</t>
+  </si>
+  <si>
+    <t>kennyoyinkansola@gmail.com</t>
+  </si>
+  <si>
+    <t>Shakirah</t>
+  </si>
+  <si>
+    <t>Manchester, England</t>
+  </si>
+  <si>
+    <t>Frontend Development Trainer</t>
+  </si>
+  <si>
+    <t>Niyo Group Ltd</t>
+  </si>
+  <si>
+    <t>HTML, CSS, JavaScript, React, Redux, Resume Review, Thinking in React, Interview Preparation</t>
+  </si>
+  <si>
+    <t>Business Analysis</t>
+  </si>
+  <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>I am looking for a mentee who is enthusiastic and curious in learning new things.</t>
+  </si>
+  <si>
+    <t>https://linkedin.com/in/sakirat-Kehinde-usman-3a4600117</t>
+  </si>
+  <si>
+    <t>https://github.com/oyinkan
+https://gitshowcase.com/oyinkan</t>
+  </si>
+  <si>
+    <t>https://calendly.com/kennyoyinkansola/the-mentoring-session-shakirah</t>
+  </si>
+  <si>
+    <t>The study group will basically focus on people that wants to learn about frontend development. Instead of speaking one to one, we can make it a group thing.</t>
+  </si>
+  <si>
+    <t>I am a student learning about data science</t>
+  </si>
+  <si>
+    <t>Ying Liu</t>
+  </si>
+  <si>
+    <t>Ying.womencodingcommunity@gmail.com</t>
+  </si>
+  <si>
+    <t>Head of AI, R&amp;D</t>
+  </si>
+  <si>
+    <t>TG0</t>
+  </si>
+  <si>
+    <t>I have a Ph.D in Physics and 4-years experience working in the field of machine learning. I published 4 papers and 2 under submission. My expertise sits in few-shot learning, CNN, Diffusion model and transformers with model architecture building using TensorFlow and PyTorch.</t>
+  </si>
+  <si>
+    <t>Software Development, Machine Learning Algorithm, Resume Review, Preparation for The Technical Interview.</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>Motivated individuals who are eager to learn the algorithms of Machine Learning</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/yingliu-data/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/ying-womencodingcommunity/30min</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Adriana Zencke Zimmermann</t>
+  </si>
+  <si>
+    <t>dricazenck@gmail.com</t>
+  </si>
+  <si>
+    <t>Valencia / Spain</t>
+  </si>
+  <si>
+    <t>Centric Software</t>
+  </si>
+  <si>
+    <t>English, Portuguese</t>
+  </si>
+  <si>
+    <t>I am a mother, a wife, and a Software Engineer. I graduated in Computer Science and have over 14 years of experience working in tech companies in Brazil, Germany, and Spain. As Backend Engineer, I found this to be my passion which I focused on in the last six years of my career. I am always excited to help others, and my goal is to empower women and support them with the difficulties I had as an engineer, and I still have from time to time.</t>
+  </si>
+  <si>
+    <t>Java, Spring Boot and Best Practices</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Someone willing to learn new technologies or to improve current skills, looking for guidance on how to navigate the initial years in the industry or in a new company. Also someone able to invest time in learning.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/dricazenck/</t>
+  </si>
+  <si>
+    <t>https://twitter.com/DricaZenck
+https://medium.com/@dricazenck
+https://github.com/dricazenck</t>
+  </si>
+  <si>
+    <t>https://calendly.com/dricazenck/mentoring</t>
+  </si>
+  <si>
+    <t>Platform Bootcamp</t>
+  </si>
+  <si>
+    <t>Fernanda Martins</t>
+  </si>
+  <si>
+    <t>flmmartins@gmail.com</t>
+  </si>
+  <si>
+    <t>Amsterdam/Netherlands</t>
+  </si>
+  <si>
+    <t>DevOps Engineer</t>
+  </si>
+  <si>
+    <t>Clay Solutions</t>
+  </si>
+  <si>
+    <t>I work with infrastructure engineering for 13 years. I love all things infrastructure: designing platforms in the cloud with Azure/AWS, coding in terraform/ansible/python/shell.., building awesome delivery pipelines and helping developers.
+I am from Brazil, currently living in Amsterdam and worked in several companies and different industries.
+I am community-driven: I have presented at conferences, contributed to open source and like sharing knowledge.</t>
+  </si>
+  <si>
+    <t>DevOps practices, how to start in infrastructure, resume review, learn cloud, infrastructure as code, incident management, improve your pipeline, manage platform priorities, how to better support developers</t>
+  </si>
+  <si>
+    <t>Dedicated, curious and thirsty for knowledge</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/flmmartins/</t>
+  </si>
+  <si>
+    <t>Find me on x, github, medium with @flmmartins</t>
+  </si>
+  <si>
+    <t>https://calendly.com/flmmartins/mentorship</t>
+  </si>
+  <si>
+    <t>I can go to a study group and help with content but I am terrible in organising the event itself.</t>
+  </si>
+  <si>
+    <t>Gabriel Oliveira</t>
+  </si>
+  <si>
+    <t>gabriel.pa.oliveira@gmail.com</t>
+  </si>
+  <si>
+    <t>gpaoliveira</t>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>Picnic</t>
+  </si>
+  <si>
+    <t>7-10 Years</t>
+  </si>
+  <si>
+    <t>I am a pragmatic Agile tester dedicated to enhancing team deliveries through the development and maintenance of automated tests, fostering cross-disciplinary collaboration to establish a unified understanding of our products, and providing timely, actionable feedback to stakeholders.
+🤔 You may be thinking "So what, how does that help me"? Or you may be in the category of "I don't know where to grow/learn next"? Book a session and tell me a bit about yourself so we can together find a way on how my experience can help you 😉
+🥶 Also, if you get frozen solid when doing test automation, I also offer an guidance on automated testing where we can deep-dive into the code of your choice together.</t>
+  </si>
+  <si>
+    <t>QA Engineering, Agile Testing, Software Test Automation</t>
+  </si>
+  <si>
+    <t>Product Management</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>QAs willing to grow on their career</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/gpaoliveira</t>
+  </si>
+  <si>
+    <t>https://calendly.com/gabriel-pa-oliveira</t>
+  </si>
+  <si>
+    <t>Samuela Smolorz</t>
+  </si>
+  <si>
+    <t>samuela.smolorz@gmail.com</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Garrison Technology Ltd</t>
+  </si>
+  <si>
+    <t>August, September, October, November</t>
+  </si>
+  <si>
+    <t>English, Polish</t>
+  </si>
+  <si>
+    <t>I am a backend/cloud infrastructure engineer specialising in database administration. Previously, I’ve worked as a data analyst/engineer. 
+Being a self-taught English graduate made my tech journey quite challenging, but it has also equipped me to help career switchers navigate today's difficult market. I feel like popular advice given to junior engineers is not necessarily applicable anymore, and I would love to share everything I have learnt with others.</t>
+  </si>
+  <si>
+    <t>- Cloud infrastructure engineering
+- Databases and SQL
+- Technical writing
+- Cybersecurity
+- Working in data vs software teams
+- Working in start-ups vs mid-sized vs big companies
+- Interview preparation
+- Personal project/resume review</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Go</t>
+  </si>
+  <si>
+    <t>Career switchers or junior engineers who would like to grow, adapt and reflect</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/samuela-smolorz-mbcs-6821a3161/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/samuela-smolorz/mentoring-session</t>
+  </si>
+  <si>
+    <t>Arzu Caner</t>
+  </si>
+  <si>
+    <t>arzuguneycaner@gmail.com</t>
+  </si>
+  <si>
+    <t>United Kingdom/London</t>
+  </si>
+  <si>
+    <t>InnoAl Tech Solution</t>
+  </si>
+  <si>
+    <t>English, Turkish</t>
+  </si>
+  <si>
+    <t>Arzu began her career in the telecommunications sector, specializing in CRM systems and marketing. After earning her master's degree in marketing, she successfully led customer loyalty and retention projects as a Marketing and Customer Relationship Manager, developing and implementing strategic campaigns aimed at enhancing customer satisfaction and loyalty. Additionally, she provided system and product training as an instructor.
+She then made significant contributions as a digital project manager, supporting the growth and development of startups, and has a strong background in SEO. With a keen interest in technological advancements, Arzu transitioned into software development, initially focusing on databases and leveraging emerging technologies to optimize data management. She currently works on mobile and web application development, where she innovates solutions to improve user experience and performance. 
+Arzu shares her career journey and technical insights through blog posts and serves as an evangelist in the Women Coding Community, actively promoting the advancement of women in technology.</t>
+  </si>
+  <si>
+    <t>Career change, app development, software development, GitHub, hackathons, technical writing, React, React Native, JavaScript, Node.js, MongoDB</t>
+  </si>
+  <si>
+    <t>Those who are changing their careers, interested in app development.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/arzucaner/</t>
+  </si>
+  <si>
+    <t>https://x.com/arz_ugny, https://arzugny.medium.com/, https://github.com/arzucaner, https://www.youtube.com/channel/UCsK0v6RouRYb5I1Ny8flrOg</t>
+  </si>
+  <si>
+    <t>https://calendly.com/arzucaner</t>
+  </si>
+  <si>
+    <t>Thank you!</t>
+  </si>
+  <si>
+    <t>Prabha Venkatesh</t>
+  </si>
+  <si>
+    <t>pvconnect10@gmail.com</t>
+  </si>
+  <si>
+    <t>Prabha</t>
+  </si>
+  <si>
+    <t>Bristol, UK</t>
+  </si>
+  <si>
+    <t>Milbotix</t>
+  </si>
+  <si>
+    <t>I am an AI Engineer with around 7 years of experience in software and a special focus on AI in the last few years. I have been leading AI research for a health care startup and have co-authored papers and a patent on the work carried out.</t>
+  </si>
+  <si>
+    <t>Individuals in early careers who are looking for help in coding and career guidance; but happy to help anyone I can</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/prabha-venkatesh-t</t>
+  </si>
+  <si>
+    <t>https://calendar.app.google/k45rqWPrHUJddBjs5</t>
+  </si>
+  <si>
+    <t>Ima-Abasi Effiong</t>
+  </si>
+  <si>
+    <t>imaabasieea@gmail.com</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Cloudenly</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>I’m a QA Engineer with over 2 years of experience in manual testing, particularly in the HR tech field. I originally studied English/Literary Studies in university but switched to IT more than two years ago. I’m passionate about helping other women like me who are also transitioning into the IT industry.</t>
+  </si>
+  <si>
+    <t>Quality Assurance, Switch career to IT, Product Management, Grow from beginner to mid level.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/imaabasieffiong/</t>
+  </si>
+  <si>
+    <t>https://x.com/eeimaabasi</t>
+  </si>
+  <si>
+    <t>https://calendly.com/imaabasieea</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Lidiane Mayra Taquehara</t>
+  </si>
+  <si>
+    <t>lidi.mayra@gmail.com</t>
+  </si>
+  <si>
+    <t>Lidiane Taquehara</t>
+  </si>
+  <si>
+    <t>Senior Software Engineer</t>
+  </si>
+  <si>
+    <t>Artsy</t>
+  </si>
+  <si>
+    <t>I'm a senior software engineer who migrated to IT after 10 years working on a complete different area (I was a factory worker in the past). I found my passion in the tech field and I'd love to help other women who are also interested in it.</t>
+  </si>
+  <si>
+    <t>Software engineering, Automated tests, Backend development, Test Driven Development, Web scraping</t>
+  </si>
+  <si>
+    <t>Ruby</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lmayra/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/lidimayra</t>
+  </si>
+  <si>
+    <t>Sergei Begishev</t>
+  </si>
+  <si>
+    <t>begishev.ss@gmail.com</t>
+  </si>
+  <si>
+    <t>Sergey Begishev</t>
+  </si>
+  <si>
+    <t>Belgrade, Serbia</t>
+  </si>
+  <si>
+    <t>Chief Product Officer</t>
+  </si>
+  <si>
+    <t>Overgear</t>
+  </si>
+  <si>
+    <t>I am a product leader with over 5 years of experience in IT, currently serving as Chief Product Officer (CPO) and building upon my engineering foundation. My experience spans both large corporations and startups, with particular strengths in analyzing business data and streamlining operations. My commitment to mentorship grew from helping engineers effectively communicate their business impact, leading me to develop and teach a course that has equipped over 20 engineers with skills to present results confidently and advance their careers. I remain dedicated to expanding this impact by continuing to guide emerging tech professionals in bridging the gap between technical excellence and business success.</t>
+  </si>
+  <si>
+    <t>Mentoring Topics: Product Architecture &amp; Design, Business Data Analysis &amp; Visualization, Team Management &amp; Leadership Skills, Technical Project Presentation, Process Automation Strategy, Cross-functional Communication</t>
+  </si>
+  <si>
+    <t>I am seeking motivated engineers who want to elevate their careers by developing their ability to communicate technical work in business terms, enhance their leadership capabilities, and master data-driven decision making</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sergey-begishev/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/begishev-ss/mentoring-session-with-sergei-begishev</t>
+  </si>
+  <si>
+    <t>I could organize a bi-weekly study group for 6-8 engineers focused on translating technical achievements into business impact, featuring hands-on exercises where participants practice presenting their project results, receive structured feedback, and learn frameworks for quantifying and communicating value to stakeholders.</t>
+  </si>
+  <si>
+    <t>he/him</t>
+  </si>
+  <si>
+    <t>Nadezhda Iaromirova</t>
+  </si>
+  <si>
+    <t>n.yaromirova@gmail.com</t>
+  </si>
+  <si>
+    <t>Bulgaria, Sofia</t>
+  </si>
+  <si>
+    <t>Aceonis</t>
+  </si>
+  <si>
+    <t>As a 360° digital marketing expert with 15+ years of experience, I would be happy to offer professional advice and provide mentorship to those at the entry-level or mid-level of their careers. My experience is primarily in enterprise-level software companies, focusing on data protection and cybersecurity. I bring expertise in web and IT-specific project management, complex technical product delivery, and web production.</t>
+  </si>
+  <si>
+    <t>I'm looking for entry-level or mid-level professionals who are eager to advance their careers in IT project management, product ownership, business analysis, or UX. If you're passionate about growing your skills, open to constructive feedback, and ready to take the next step in your career, I'd love to provide personalized mentorship and career advice.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/yaromirova/</t>
+  </si>
+  <si>
+    <t>https://hackernoon.com/u/uxdilettante</t>
+  </si>
+  <si>
+    <t>https://calendly.com/n-yaromirova</t>
+  </si>
+  <si>
+    <t>Our study groups can cover a range of engaging topics, such as a User Experience Research Workshop, roundtable discussions on overcoming FOMO and/or impostor syndrome, and sessions sharing practical project management hacks.</t>
+  </si>
+  <si>
+    <t>Kateryna Ogar</t>
+  </si>
+  <si>
+    <t>katerynaogar@gmail.com</t>
+  </si>
+  <si>
+    <t>Product Manager/ Scrum Master</t>
+  </si>
+  <si>
+    <t>Cisco Systems</t>
+  </si>
+  <si>
+    <t>English, Russian, Ukranian</t>
+  </si>
+  <si>
+    <t>Hi there! I’m Kateryna, a Product Manager and Scrum Master with 5+ years of hands-on experience driving innovation and delivering complex software solutions for industry leaders like NASDAQ, Ericsson, and Volvo. My certifications in PSM1, KSP, and SAFe 5.1 Agilist reflect my commitment to delivering top-quality results using Agile, Kanban, Lean, TDD, and BDD practices.
+As a mentor, I’m here to guide you through the challenges of product management, project leadership, and Agile practices. Whether you're looking to improve team performance, navigate complex projects, or refine your leadership skills, I’m passionate about helping you grow.
+I’m also a proud mentor in the Women in Tech (6.0) program and am ranked in the Top 1% of Product Mentors on ADPList, where I’ve helped mentees like you unlock their full potential, drive innovations and secure new jobs. If you're ready to take your career to the next level and make an impact in tech, let’s work together to shape your journey!</t>
+  </si>
+  <si>
+    <t>Product Management, Project Management, Agile &amp; Scrum Practices, Diversity &amp; Inclusion in Tech, Career Development &amp; Leadership, Resume Review, Interview Mock Sessions</t>
+  </si>
+  <si>
+    <t>I’m looking to work with motivated individuals who are excited to grow their skills in product/project management and leadership. If you’re looking to transition into product/project management, step into a leadership role in Agile teams or improve your skills, I’d love to help you get there!
+I enjoy mentoring curious learners who want to dive into Agile methodologies like Scrum, Kanban, and SAFe. If you’re passionate about creating products that make a real impact and aligning your work with business goals, we’ll be a great match.
+If you’re ready to take your career to the next level, let’s connect and make it happen!</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kateryna-ogar/</t>
+  </si>
+  <si>
+    <t>https://adplist.org/mentors/kateryna-ogar</t>
+  </si>
+  <si>
+    <t>https://calendly.com/kogar-cisco/1-hour-consultation</t>
+  </si>
+  <si>
+    <t>Wilson Adenuga</t>
+  </si>
+  <si>
+    <t>oluwatunmiseadenuga@gmail.com</t>
+  </si>
+  <si>
+    <t>UK/Birmingham</t>
+  </si>
+  <si>
+    <t>Senior Frontend Engineer</t>
+  </si>
+  <si>
+    <t>BeyondIT SRL</t>
+  </si>
+  <si>
+    <t>May, June, July</t>
+  </si>
+  <si>
+    <t>I am a full-stack engineer specializing in building scalable, accessible web and mobile applications. My expertise spans React.js, React Native, Next.js, Node.js, Python, microservices, and cloud platforms like AWS and Cloudflare. I've led projects in fintech, healthcare, and cybersecurity domains. I'm passionate about mentoring developers, improving code quality, and advocating for best practices in TDD, database design, and web accessibility. I actively contribute to the developer community through mentorship programs and open-source projects.</t>
+  </si>
+  <si>
+    <t>Full-Stack JavaScript Development (React.js, Next.js, Node.js)
+Mobile App Development with React Native
+Test-Driven Development Methodologies
+Technical Interview Preparation
+Web Accessibility Best Practices
+Python Programming Fundamentals</t>
+  </si>
+  <si>
+    <t>I'm looking for mentees who are passionate, eager to learn, and committed to upskilling. I can provide mentorship in backend and frontend engineering, test-driven development (TDD), database design, microservices, system design, and emerging topics in software engineering.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/wilson-adenuga/</t>
+  </si>
+  <si>
+    <t>https://x.com/Adenugawilson, https://github.com/oluwatunmiisheii</t>
+  </si>
+  <si>
+    <t>https://calendly.com/oluwatunmiseadenuga/mentorship-session-with-wilson-adenuga</t>
+  </si>
+  <si>
+    <t>A study group focused on web accessibility, testing best practices, and emerging technologies like NFC. Sessions will include hands-on coding exercises, discussions on real-world implementation, and knowledge-sharing on improving inclusive web development.</t>
+  </si>
+  <si>
+    <t>Sebastian Castro</t>
+  </si>
+  <si>
+    <t>sebas.a.castro@gmail.com</t>
+  </si>
+  <si>
+    <t>Boston, MA, USA</t>
+  </si>
+  <si>
+    <t>Robotics Software Engineer</t>
+  </si>
+  <si>
+    <t>Robotics and AI Institute</t>
+  </si>
+  <si>
+    <t>English, Spanish</t>
+  </si>
+  <si>
+    <t>I began my career as a technical support/training/education marketing engineer focused on robotics and simulation. At the start of 2020, I made a full transition to robotics software engineering and have been keeping up with this challenging career while also tapping into my education interests through open-source software and mentorship projects. Learn more about me at https://roboticseabass.com/about/.</t>
+  </si>
+  <si>
+    <t>Robotics, Software Engineering, Machine Learning, Simulation, Education</t>
+  </si>
+  <si>
+    <t>Rust</t>
+  </si>
+  <si>
+    <t>I am looking to help people interested in the robotics field, specially focused on open-source software and/or educational content development. My specialties in robotics include high-level behavior, task and motion planning, and manipulation, but I am willing to branch out and learn with you!</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sebastian-a-castro</t>
+  </si>
+  <si>
+    <t>https://bsky.app/profile/roboticseabass.com</t>
+  </si>
+  <si>
+    <t>https://calendly.com/sebas-a-castro/30min</t>
+  </si>
+  <si>
+    <t>Ramona Gawarwala</t>
+  </si>
+  <si>
+    <t>ramona.mironescu@gmail.com</t>
+  </si>
+  <si>
+    <t>Software Engineer II</t>
+  </si>
+  <si>
+    <t>Discovery Education</t>
+  </si>
+  <si>
+    <t>May, June, July, August, September, October, November</t>
+  </si>
+  <si>
+    <t>English, Romanian</t>
+  </si>
+  <si>
+    <t>I started my career in healthcare, but six years ago, I made the switch to software development after completing a bootcamp. It was one of the best decisions I’ve ever made. Since then, I’ve worked as a Software Developer, continuously learning and growing, and now I’m on my way to becoming a Senior Engineer with a strong interest in cybersecurity and software architecture. I love solving complex problems, building secure and scalable applications, and finding ways to improve systems. I thrive in collaborative environments, enjoy sharing what I learn, and always look for ways to make tech more efficient and accessible. To further develop my skills, I completed the Mid-Level Accelerator course with Code First Girls, and I’m currently enrolled in a GenAI bootcamp to understand both the landscape and boundaries of Generative AI. Through this, I’m learning how to critically think, troubleshoot, and build real-world GenAI workloads. One of the most valuable lessons I’ve learned in my tech journey is the power of mentorship and networking—especially as a woman in tech. Early on, I realized that even if we don’t always see many women around us at work, we are not alone. There is a whole community of women who have gone through the same challenges, faced impostor syndrome, and needed support to stay motivated. Seeing this has made me passionate about encouraging more women not just to enter tech, but to stay in the field, find meaning in their work, and recognize the immense value they bring to the table. Outside of work, I’m into hiking, photography, and getting lost in a good book. I also explore topics like digital transformation, organizational psychology, and the intersection of tech and human behavior—it’s fascinating how technology shapes the way we work and interact. My journey into tech was anything but traditional, and I know how challenging (and rewarding) career changes can be. That’s why I love connecting with others who are navigating similar paths and sharing what I’ve learned along the way.</t>
+  </si>
+  <si>
+    <t>Motivated and proactive</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ramona-gawarwala/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/ramona-gawarwala</t>
+  </si>
+  <si>
+    <t>She/her</t>
+  </si>
+  <si>
+    <t>Sonika Janagill</t>
+  </si>
+  <si>
+    <t>sonika.janagill@gmail.com</t>
+  </si>
+  <si>
+    <t>Sonika</t>
+  </si>
+  <si>
+    <t>Watford</t>
+  </si>
+  <si>
+    <t>Engineering Advocate</t>
+  </si>
+  <si>
+    <t>VML</t>
+  </si>
+  <si>
+    <t>English, Hindi, Punjabi</t>
+  </si>
+  <si>
+    <t>Experienced technology professional with 18+ years spanning Java development, e-commerce solutions, cloud architecture, and AI engineering. Currently serving as an Engineering Advocate at VML and Data Engineer at Satalia, I bridge enterprise systems with cutting-edge AI technologies.
+My journey includes leading complex e-commerce implementations, cloud, and AI innovations. As a certified GCP Professional Architect and Scrum Master, I combine technical expertise with strategic vision.
+Passionate about empowering developers to embrace AI and promoting diversity in tech, I leverage my background across multiple technologies to connect diverse domains and drive innovative solutions.</t>
+  </si>
+  <si>
+    <t>Cloud Architecture &amp; Data Engineering
+CI/CD using Infra As Code
+AI Engineering &amp; Implementation Strategies
+Transitioning from Traditional Development to AI/ML
+Enterprise E-commerce Solutions
+Technical Career Path Evolution &amp; Growth
+Balancing Technical Depth &amp; Business Awareness
+Building Technical Advocacy Skills
+Work-Life Balance in Technical Careers</t>
+  </si>
+  <si>
+    <t>I'm seeking curious, proactive individuals interested in AI, data engineering, or modern software development. Whether you're transitioning from traditional development to AI/ML, looking to enhance your cloud architecture skills, or aiming to grow as a technical leader, I'd be delighted to support you. I particularly welcome those with clear goals, a commitment to consistent learning. I especially encourage women and underrepresented groups in tech who are navigating technical career paths.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sonikaj/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/sonika-janagill</t>
+  </si>
+  <si>
+    <t>Cloud certification, AI agents, RAG etc.</t>
+  </si>
+  <si>
+    <t>Prerna Singhal</t>
+  </si>
+  <si>
+    <t>prerna.singhal90@gmail.com</t>
+  </si>
+  <si>
+    <t>London, United Kingdom</t>
+  </si>
+  <si>
+    <t>Senior Software Engineer 2</t>
+  </si>
+  <si>
+    <t>Hubspot</t>
+  </si>
+  <si>
+    <t>Currently working as Lead Engineer for Hubspot. I have 12 years for Software development experience (Backend and Fullstack). I have worked with tech giants for 7 years - Microsoft, Expedia, Salesforce and have worked in startup industry for 5 years. Hence i understand working in both in environments. I have worked with wide variety of technologies - Java, AWS, Azure, Python, Distributed systems, Scaling applications.</t>
+  </si>
+  <si>
+    <t>Software Development Strategies, Resume Review, Preparation for The Technical Interview, How to grow from junior to lead engineers, Project management</t>
+  </si>
+  <si>
+    <t>One who wants to transition from junior to senior levels.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/prernasinghal90/</t>
+  </si>
+  <si>
+    <t>https://topmate.io/prerna_singhal</t>
+  </si>
+  <si>
+    <t>ilayda yilmaz</t>
+  </si>
+  <si>
+    <t>yyilmazilayda@gmail.com</t>
+  </si>
+  <si>
+    <t>ilayday</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Data Scientist</t>
+  </si>
+  <si>
+    <t>GDZ</t>
+  </si>
+  <si>
+    <t>I have been working in the tech industry for 5 years and am currently building my career in the data field. My experience spans across data science projects such as predictive modeling, anomaly detection, and time series forecasting. With a background in software development, I enjoy combining technical skills with data-driven thinking to solve real-world problems. I'm passionate about helping others who are also transitioning into data science.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to focus on when transitioning into data science
+Building a roadmap for becoming a Data Scientist
+Technical interview preparation for data roles
+Resume and LinkedIn review for aspiring data professionals
+Working on portfolio projects and showcasing them effectively
+Communicating data insights clearly to different audiences
+</t>
+  </si>
+  <si>
+    <t>I'm looking for a mentee who is curious, motivated, and open to feedback. Ideally, someone who is either transitioning into the data field or already on their way and looking for guidance on how to grow. I’d love to work with someone who’s willing to explore ideas, ask questions, and take initiative in their learning journey.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ilayda-yilmaz/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/yyilmazilayda/30min</t>
+  </si>
+  <si>
+    <t>Damola Taiwo</t>
+  </si>
+  <si>
+    <t>Frontend system design interview preparation and strategies
+Preparing for technical interviews (Frontend focus)
+Resume review and feedback
+Transitioning into a frontend development career</t>
+  </si>
+  <si>
+    <t>Dan Antonela</t>
+  </si>
+  <si>
+    <t>dan.antonela@gmail.com</t>
+  </si>
+  <si>
+    <t>I have joined Slack community</t>
+  </si>
+  <si>
+    <t>Cluj-Napoca, Romania</t>
+  </si>
+  <si>
+    <t>Data Architect</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>I bring over 12 years of experience in working with data, with a strong focus on transforming client data into actionable value. My expertise spans the full data lifecycle—from understanding business requirements and designing solutions to implementing robust data pipelines and analytics.
+Throughout my career, I have led cross-functional teams in delivering end-to-end data migration projects, particularly in transitioning solutions from on-premises environments to the cloud. My recent work has centered on leveraging Databricks technologies to design scalable, efficient, and secure data architectures that support advanced analytics and business intelligence initiatives.
+As a mentor, I aim to share not only my technical expertise but also my experience in leading teams, managing complex projects, and aligning technical solutions with business objectives. My goal is to help mentees develop both their technical skills and strategic thinking to succeed in data-driven roles.</t>
+  </si>
+  <si>
+    <t>I’m looking to mentor individuals who are eager to grow their careers in the data field, open to feedback, and committed to putting learning into action. I value mentees with a curious mindset, a strong willingness to learn, and the motivation to explore new challenges. A growth mindset, reliability, and a proactive attitude are essential—I’ll provide guidance and support, but real progress comes from those who take initiative, follow through, and are ready to push themselves.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/morar-antonela</t>
+  </si>
+  <si>
+    <t>Mudit Maheshwari</t>
+  </si>
+  <si>
+    <t>mudit94@gmail.com</t>
+  </si>
+  <si>
+    <t>London , United Kingdom</t>
+  </si>
+  <si>
+    <t>Quality Automation Specialist</t>
+  </si>
+  <si>
+    <t>NatWest Group</t>
+  </si>
+  <si>
+    <t>September, October</t>
+  </si>
+  <si>
+    <t>I’m a Quality Engineer with over six years of experience in test automation, passionate about building reliable, high-quality software that delivers a great user experience. I specialise in designing and maintaining automation frameworks using modern tools like Cypress, Playwright, and TypeScript, and I enjoy collaborating closely with developers to embed quality into every stage of delivery. I’m motivated by solving complex problems, mentoring others, and continuously improving processes. Outside of work, I’m deeply interested in investing and financial technology,</t>
+  </si>
+  <si>
+    <t>Resume Review , Latest testing tools, Top trending tech</t>
+  </si>
+  <si>
+    <t>Passionate , Patient , Hunger to learn</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/maheshwarimudit/</t>
+  </si>
+  <si>
+    <t>https://medium.com/@mudit94</t>
+  </si>
+  <si>
+    <t>https://calendly.com/mudit94</t>
+  </si>
+  <si>
+    <t>He/him</t>
+  </si>
+  <si>
+    <t>Tuğçe Kızılçakar</t>
+  </si>
+  <si>
+    <t>tugcekizilcakar@gmail.com</t>
+  </si>
+  <si>
+    <t>Tugce Kizilcakar</t>
+  </si>
+  <si>
+    <t>Istanbul</t>
+  </si>
+  <si>
+    <t>Technical Product Manager</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>October, November</t>
+  </si>
+  <si>
+    <t>With more than 10 years in tech and product management, I’ve worked on mobile payment products and agile transformation projects that reached millions of users. I enjoy helping teams improve their delivery processes and supporting young professionals who want to grow in product and tech. I’ve also mentored in several startup and education programs, sharing both technical and leadership experience.</t>
+  </si>
+  <si>
+    <t>Agile &amp; Scrum fundamentals for product and engineering teams
+Mobile app product lifecycle and MVP planning
+Communication and collaboration with technical teams</t>
+  </si>
+  <si>
+    <t>I’m looking for mentees who are passionate about growing in tech or product management — whether they’re just starting out or already have some experience. I enjoy supporting women who are curious, open to learning, and ready to take the next step in their careers. My goal is to help them gain confidence, structure their growth, and feel empowered in the tech world.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tu%C4%9F%C3%A7e-k%C4%B1z%C4%B1l%C3%A7akar-535a1a4b/</t>
+  </si>
+  <si>
+    <t>This study group will be a supportive and inspiring space for women who want to grow in tech and product management. I want to create an environment where mentees feel safe to ask questions, share experiences, and learn from real projects. We’ll focus on practical skills, confidence building, and career growth — but also on community and encouragement.</t>
+  </si>
+  <si>
+    <t>Marjorie Martinez</t>
+  </si>
+  <si>
+    <t>marjoriemartinezdev@gmail.com</t>
+  </si>
+  <si>
+    <t>Marj Martinez</t>
+  </si>
+  <si>
+    <t>Software Developer</t>
+  </si>
+  <si>
+    <t>Major Digital</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>English, Filipino</t>
+  </si>
+  <si>
+    <t>Frontend-focused software developer with 6+ years of experience working on web applications for multinational clients, focusing on reliability, maintainability, and user experience. Experienced in building accessible interfaces, implementing authentication flows, and migrating legacy projects to modern frontend solutions. Motivated by improving complex systems and contributing to products that evolve over time.</t>
+  </si>
+  <si>
+    <t>Software Development Strategies, Resume Review, Career Transition, Career Path Guide</t>
+  </si>
+  <si>
+    <t>Somewhere beginner level or mid level that's looking for career guide</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/marjorie-martinez/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/marjoriemartinezdev/30min</t>
+  </si>
+  <si>
+    <t>She</t>
+  </si>
+  <si>
+    <t>Faith Sodipe</t>
+  </si>
+  <si>
+    <t>faithsodipe@gmail.com</t>
+  </si>
+  <si>
+    <t>United Kingdom / Manchester</t>
+  </si>
+  <si>
+    <t>I am a software engineer with half a decade of professional experience building scalable, production-grade systems across fintech, banking, digital media, and data-driven platforms. My technical background spans backend engineering with C# and .NET, cloud-native architectures on Azure, event-driven microservices, distributed systems, and cross-platform mobile development using Flutter. I’ve worked on systems that support real users at scale, handle sensitive data, and generate revenue, with a strong focus on clean architecture, performance, security, and resilience.
+Beyond delivery, I’ve taken ownership of system design decisions, collaborated closely with product and engineering leaders, and contributed to improving reliability, monitoring, and developer experience. I also hold an MSc in Cybersecurity, which informs my approach to building secure, trustworthy software.
+I’m deeply passionate about mentorship and community impact. I’ve supported career switchers, junior developers, and beginners through one-on-one mentoring, speaking engagements, and community sessions. My goal as a mentor is to help mentees build strong technical foundations, confidence, and clarity in their career paths, while encouraging curiosity, persistence, and continuous learning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Design Fundamentals, Preparation for Technical Interviews, Soft Skills Beyond Technical Ability, Resume Review, Software Development Lifecyle, Agile Methodologies, Cybersecurity Essentials, Lessons Learned in Building systems at scale, System Optimization Strategies, Growing as an Engineer, AI, General Career advice
+</t>
+  </si>
+  <si>
+    <t>Dart</t>
+  </si>
+  <si>
+    <t>I am looking for mentees who are curious, open to learning, and willing to show up consistently, regardless of their current skill level. You don’t need to have everything figured out, what matters most is a genuine interest in growing, asking questions, and reflecting on feedback. I particularly enjoy working with early-career developers and career switchers who may be navigating confidence gaps or uncertainty and who want guidance on building strong foundations in both technical skills and professional growth. I value honesty, communication, and a collaborative mindset, and I aim to create a supportive, judgment-free space where mentees feel comfortable making mistakes and learning from them. If you’re motivated to learn, willing to put in the effort, and open to exploring your potential in tech, we’ll work well together.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sodipefaith/</t>
+  </si>
+  <si>
+    <t>https://medium.com/@faithsodipe</t>
+  </si>
+  <si>
+    <t>https://calendly.com/faithsodipe</t>
+  </si>
+  <si>
+    <t>The study group would be a small, structured learning group focused on building strong software engineering foundations in a supportive and collaborative environment. Sessions would run on a fixed schedule (for example, once every two weeks) with clearly defined goals for each meeting to ensure time commitments remain manageable. Each session would combine guided discussion, practical exercises, and Q&amp;A, rather than lectures, encouraging participants to actively engage and learn from one another.
+The group would focus on early-career topics such as programming fundamentals, problem-solving, version control, basic system design concepts, and career development in tech. Resources and tasks would be shared ahead of sessions so participants can prepare, and progress can be tracked without requiring additional ad-hoc meetings. My role would be to facilitate discussions, provide guidance, and support participants’ learning, while encouraging peer-to-peer collaboration. This approach ensures consistent impact, clear boundaries on time commitment, and a sustainable format for everyone involved.</t>
+  </si>
+  <si>
+    <t>goragottsen@gmail.com</t>
+  </si>
+  <si>
+    <t>@Ana Roldugina</t>
+  </si>
+  <si>
+    <t>Full Stack Engineer</t>
+  </si>
+  <si>
+    <t>Count Ltd. (Record OS)</t>
+  </si>
+  <si>
+    <t>Full-stack engineer with 5+ years of experience building scalable web applications in startup and product-driven environments. I specialize in React/TypeScript on the frontend and Python or PHP on the backend, with a strong focus on clean architecture, reliability, and user-centric design.
+I’ve led and delivered end-to-end features from concept to production, including complex third-party integrations, automation systems, and data-heavy workflows. I enjoy working across the stack, collaborating closely with product and design, and turning ambiguous ideas into practical, high-impact solutions.</t>
+  </si>
+  <si>
+    <t>Working in startups: ownership, prioritisation, shipping with limited resources, Turning product requirements into technical solutions, Third-party integrations (email systems, e-signatures, external APIs), Technical interview preparation (frontend, full-stack, take-home tasks, pair programming), CV / resume review for software engineers</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/anaroldugina/</t>
+  </si>
+  <si>
+    <t>https://calendly.com/goragottsen/60min</t>
+  </si>
+  <si>
+    <t>Srinivasulu Paranduru</t>
+  </si>
+  <si>
+    <t>srinivasulup.538034@gmail.com</t>
+  </si>
+  <si>
+    <t>Letterkenny, Ireland</t>
+  </si>
+  <si>
+    <t>AWS Solution &amp; Senior Devops</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t>June, July, August, September, October, November</t>
+  </si>
+  <si>
+    <t>English, Telugu,Tamil</t>
+  </si>
+  <si>
+    <t>Having close to 20 years of IT Experience and delivered multiple projects and worked in multiple locations. I am a Microsoft Certified Trainer, AWS User Group Leader and AWS Community Builder,GDG Letterkenny Organizer.</t>
+  </si>
+  <si>
+    <t>Software Development (Python,C#,Cloud Skills), Preparation for Interviews</t>
+  </si>
+  <si>
+    <t>Need Mentee who are focused and willing to learn and scale up their skills</t>
+  </si>
+  <si>
+    <t>https://calendly.com/srinivasuluparanduru</t>
+  </si>
+  <si>
+    <t>I am a Platinum Certified from TCS , Global Initiative Mentor helping students across UN</t>
+  </si>
+  <si>
+    <t>Aria Wright</t>
+  </si>
+  <si>
+    <t>ariaandromedawright@gmail.com</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>Build Engineer</t>
+  </si>
+  <si>
+    <t>RAI Institute</t>
+  </si>
+  <si>
+    <t>I'm a newly minted build engineer and have experience in software and robotics for 4 years. I've worked for extremely small startups and large-scale biotech companies. My background is eclectic, ranging from devops and data engineering to underwater vehicles and AR/VR.</t>
+  </si>
+  <si>
+    <t>Someone who has had a similarly eclectic career path or who is looking to grow from junior/mid-level to senior engineer</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/aria-andromeda</t>
+  </si>
+  <si>
+    <t>Airah Yusuff</t>
+  </si>
+  <si>
+    <t>airahyusuff@gmail.com</t>
+  </si>
+  <si>
+    <t>Airah Y.</t>
+  </si>
+  <si>
+    <t>Cloud Engineer</t>
+  </si>
+  <si>
+    <t>Trainline</t>
+  </si>
+  <si>
+    <t>June, July, August, September, October</t>
+  </si>
+  <si>
+    <t>English, Yoruba</t>
+  </si>
+  <si>
+    <t>I currently work as a Cloud Platform Engineer, where I focus on leveraging cloud technologies, automation tools, and DevOps practices to build systems and tooling that help developers worry less about how to continuously deploy and monitor their applications in production.
+Prior to transitioning fully into cloud engineering, I worked as a Software Engineer for about four years across startup and consulting environments, gaining hands-on experience in frontend and backend development using technologies such as JavaScript/TypeScript, Node.js, and Java.
+As a mentor, I aim to support engineers who want to transition into cloud roles, strengthen their understanding of cloud fundamentals, and build confidence working with AWS, automation, and CI/CD practices.
+Outside of work, I am a fourth-year AWS Community Builder, a Lead at Women Coding Community, and I regularly document my cloud journey and new learnings through technical articles on my blog.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Fundamentals
+Transitioning into Cloud/DevOps Roles
+AWS Community Builders Program
+CV Reviews for Junior cloud roles
+UK Global Talent Visa discussions
+</t>
+  </si>
+  <si>
+    <t>Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t>Network Engineering</t>
+  </si>
+  <si>
+    <t>I'm looking to work with mentees who want to:
+1) transition into cloud roles
+2) strengthen their knowledge of cloud and AWS fundamentals
+3) join the AWS Community Builders program and get support with their applications
+4) know more about the UK Global Talent visa and whether it might be a right fit for them
+I’m still growing as a mentor myself, but I’m committed to doing my best to support mentees and share what I’ve learned along the way.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/khairah-yusuff/</t>
+  </si>
+  <si>
+    <t>https://github.com/khairahscorner
+https://khairahscorner.hashnode.dev</t>
+  </si>
+  <si>
+    <t>https://calendar.app.google/HdqMFb3Scnat2N8E9</t>
+  </si>
+  <si>
+    <t>She/Her</t>
+  </si>
+  <si>
+    <t>For the "programming languages" question, please use this answer instead:
+HCL (Terraform/OpenTofu), Rego, YAML, Bash, Python (for scripting)</t>
+  </si>
+  <si>
+    <t>Michelle Victora</t>
+  </si>
+  <si>
+    <t>michelle4654@gmail.com</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts, USA</t>
+  </si>
+  <si>
+    <t>I'm a robotics software engineer with a PhD in quantum physics and 5 years of industry experience. I've worked at Aliro Quantum Technologies (quantum networking), RightHand Robotics (warehouse automation), and currently at a robotics AI institute developing execution code and platforms to support on-robot policy learning.
+Technical expertise: Quantum optics, quantum networks, Python, ROS 2, Lightweight Communications and Marshalling (LCM), hierarchical state machines, motion planning algorithms, hardware-software integration. Experience spans from experimental quantum optics to robotic manipulation and motion planning.
+Notable projects: Reduced production motion planning failures 50% through algorithmic improvements; developed grasping algorithms with &gt;10x damage reduction validated through A/B testing on customer sites; architected ROS 2 Control hardware interfaces enabling diffusion policy execution on robotic hardware, translated C++ executor to Python, enabling additional features to support RL policy deployment, built metrics evaluation pipeline for sim-&gt;sim-&gt;real policy evaluation.
+I'm particularly interested in helping mentees with: transitioning from research/academia to industry (and back), gathering requirements for production systems, technical interview preparation, and navigating early-to-mid career growth in robotics/AI.</t>
+  </si>
+  <si>
+    <t>Career Transitions &amp; Growth:
+*Navigating career pivots (quantum physics → robotics, research → production)
+*Growing from junior to mid-level engineer
+*Dealing with imposter syndrome when changing domains
+*Deciding between startup vs research lab
+Technical Interview Preparation:
+*Coding interview strategies and practice (algorithms, data structures)
+*System design discussions (component-level architecture)
+*Behavioral interviews 
+*Talking about your work effectively in interviews
+Software Development:
+*Writing production-quality code (vs research code)
+*Working with hardware-software integration
+Robotics-Specific:
+*ROS 2 development and best practices
+*Writing executors and motion planning algorithms
+*Working with research teams as an engineer</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/michelle-victora-a3a49851/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/michellevictora/, https://www.facebook.com/mvictora</t>
+  </si>
+  <si>
+    <t>m.m.victora@gmail.com</t>
+  </si>
+  <si>
+    <t>Hersi Kopani</t>
+  </si>
+  <si>
+    <t>hersi.kopani@gmail.com</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>Walgreens Boots Alliance</t>
+  </si>
+  <si>
+    <t>Long-Term Format only</t>
+  </si>
+  <si>
+    <t>I'm a seasoned Java developer with more than five years of experience specializing in the design and implementation of robust software solutions. Throughout my tenure at many companies, I've had the privilege of spearheading pivotal projects that have played integral roles in the company's expansion. These endeavors demanded not only technical proficiency but also keen problem-solving skills and effective risk management strategies.
+In my role, I've collaborated closely with architects during the design, architecture, and implementation phases, ensuring that our deliverables consistently meet the highest standards and adhere to industry best practices. Moreover, I've cultivated strong relationships with senior stakeholders both internally and externally, leveraging these connections to gain valuable insights and contribute to the development of innovative solutions.
+Beyond my professional endeavors, I'm deeply passionate about fostering diversity and inclusion in the tech industry, particularly in empowering women to pursue and excel in STEM fields. I firmly believe that a diverse workforce leads to greater innovation and success, and I actively support initiatives aimed at bridging the gender gap in technology.
+In addition to my dedication to software development, I'm an avid tennis enthusiast, finding solace and rejuvenation on the court in my spare time. This passion for tennis not only provides a welcome escape from the demands of work but also serves as a source of inspiration and motivation, fueling my drive to continuously learn and grow both personally and professionally.
+Overall, I bring a unique blend of technical expertise, leadership acumen, and a commitment to diversity and personal enrichment to every project and endeavor I undertake.</t>
+  </si>
+  <si>
+    <t>As a mentor, I am seeking a mentee who possesses a genuine passion for coding and a sincere desire to leverage their technical skills to make a positive impact on society. I am eager to work with individuals who not only excel in coding but also exhibit a strong sense of social responsibility and an ambition to contribute to meaningful change through technology. I value enthusiasm, dedication, and a willingness to learn and grow, and I am excited to support a mentee who shares these qualities and aspirations.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/hersi-kopani/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://calendly.com/hersi-kopani </t>
+  </si>
+  <si>
+    <t>By assuming that the group would be interested to pass from junior to mid-senior level below is a detailed plan for a group of people. Very similar could be customized for group of mentees who want to start their career in TECH. Title: Advanced Software Development Study Group
+Duration: 10 weeks (1 topic per week)
+Meeting Frequency: Once a week, for 2 hours per session
+Study Material: Online resources, articles, tutorials, and coding exercises
+Tools: Git, IDE (Integrated Development Environment), cloud computing platform (e.g., AWS, Azure), testing frameworks (e.g., JUnit), and relevant programming languages and frameworks
+Week 1: Coding Best Practices
+Theoretical Concepts:
+Introduction to coding standards and conventions
+Understanding the importance of code readability and maintainability
+Exploring techniques for writing clean and efficient code
+Hands-on Practice:
+Code review session: Each participant shares a piece of code for review, focusing on adherence to coding standards and best practices.
+Refactoring exercise: Participants work on refactoring a code snippet to improve readability and maintainability.
+Week 2: Version Control Systems (VCS)
+Theoretical Concepts:
+Introduction to Git and basic commands (clone, add, commit, push, pull)
+Branching strategies (feature branches, release branches)
+Resolving merge conflicts and collaborating with teams
+Hands-on Practice:
+Setting up a Git repository: Participants create a new repository, add files, commit changes, and push to a remote repository (e.g., GitHub).
+Branching exercise: Participants practice creating and merging branches to implement a feature.
+Week 3: Software Architecture Design
+Theoretical Concepts:
+Understanding architectural patterns (MVC, RESTful APIs, microservices)
+Design principles (SOLID principles, DRY, KISS)
+Making architectural decisions based on project requirements
+Hands-on Practice:
+Design discussion: Participants analyze a given scenario and propose a suitable architecture.
+Implementing design patterns: Participants choose a design pattern and apply it to a small coding exercise.
+Week 4: Performance Optimization
+Theoretical Concepts:
+Identifying performance bottlenecks (CPU, memory, disk I/O)
+Techniques for optimizing code performance (caching, lazy loading)
+Tools for performance profiling and monitoring (JProfiler, VisualVM)
+Hands-on Practice:
+Performance profiling: Participants use a profiling tool to identify performance bottlenecks in a sample application.
+Optimization exercise: Participants work on optimizing a piece of code to improve its performance.
+Week 5: Security Practices in Development
+Theoretical Concepts:
+Common security vulnerabilities (SQL injection, XSS, CSRF)
+Secure coding practices (input validation, parameterized queries)
+Implementing security measures at different layers (network, application, data)
+Hands-on Practice:
+Security review: Participants analyze a codebase for potential security vulnerabilities and suggest improvements.
+Implementing secure coding practices: Participants refactor code to incorporate input validation and prevent common security vulnerabilities.
+Week 6: Testing Strategies
+Theoretical Concepts:
+Types of testing (unit testing, integration testing, end-to-end testing)
+Writing testable code and test-driven development (TDD)
+Testing frameworks and tools (JUnit, Mockito, Selenium)
+Hands-on Practice:
+Writing unit tests: Participants write unit tests for a sample class using JUnit.
+Test automation: Participants automate browser tests using Selenium for a simple web application.
+Week 7: Continuous Integration/Continuous Deployment (CI/CD)
+Theoretical Concepts:
+Introduction to CI/CD pipelines
+Setting up automated builds, tests, and deployments
+Tools for CI/CD (Jenkins, Travis CI, GitHub Actions)
+Hands-on Practice:
+Setting up a CI/CD pipeline: Participants configure a CI/CD pipeline for a sample project hosted on GitHub.
+Automated deployment: Participants set up automated deployment to a cloud platform (e.g., AWS, Azure) using CI/CD.
+Week 8: Scalability and Performance
+Theoretical Concepts:
+Strategies for designing scalable systems (horizontal scaling, vertical scaling)
+Load balancing and caching techniques
+Monitoring and optimizing system performance
+Hands-on Practice:
+Load testing: Participants use a load testing tool (e.g., JMeter) to simulate heavy traffic and analyze system performance.
+Implementing caching: Participants add caching to a sample application to improve performance.
+Week 9: Cloud Computing Technologies
+Theoretical Concepts:
+Overview of cloud computing models (IaaS, PaaS, SaaS)
+Popular cloud platforms (AWS, Azure, Google Cloud)
+Deploying and scaling applications in the cloud
+Hands-on Practice:
+Deploying to the cloud: Participants deploy a sample application to a cloud platform (e.g., AWS EC2, Azure App Service).
+Scaling resources: Participants configure auto-scaling for an application to handle varying loads.
+Week 10: Emerging Technologies and Trends
+Theoretical Concepts:
+Introduction to emerging technologies (AI, machine learning, blockchain)
+Potential applications of emerging technologies in software development
+Staying updated and continuous learning in the tech industry
+Hands-on Practice:
+Exploring AI/ML: Participants experiment with a simple machine learning model using a Python library like TensorFlow or scikit-learn.
+Brainstorming session: Participants discuss potential applications of emerging technologies in future projects and explore resources for continuous learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java	</t>
+  </si>
+  <si>
+    <t>I am a frontend engineer with over 3 years of experience in frontend development. I am excellent at building user interfaces and bringing  web functionalities to life. I have worked on various projects ranging from fintech to agriculture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Lead </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank you team! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal and professional development:
+https://www.developing.dev/ 
+https://www.thecaringtechie.com/ 
+https://yougotthis.io/
+Blogs:
+https://jvns.ca/
+https://chelseatroy.com/
+Job boards and programmes:
+https://www.niya.ai/ 
+https://jobs.codebar.io/
+https://www.brightnetwork.co.uk/ 
+https://targetjobs.co.uk/ 
+https://www.seo-london.org/programmes-industries
+https://www.theforage.com/simulations 
+Open source:
+https://eddiehub.org/ 
+https://www.outreachy.org/ 
+Youtube talks:
+https://www.youtube.com/watch?v=ounEy_YSwi4 
+https://www.youtube.com/watch?v=0kO2luXmn4w&amp;t=677s 
+https://www.youtube.com/watch?v=tQhhRu8cqto&amp;t=2680s </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data scientist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/ ML concepts, Resume review, technical interview </t>
+  </si>
+  <si>
+    <t>I can  provide guidance and resources to a  passionate self learner, an early career engineer and people who just switched from different fields to Software Testing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A mentee with a curious mind and passionate about learning new things.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yaromirova </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. IT Project Manager </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I can advice on a career as a project manager, product owner, or business analyst. I also specialize in user experience (UX) optimization, A/B testing, digital analytics, and reporting and can consult on UX and UI topics. Also, I can offer guidance on Agile methodologies widely used in IT, insights into valuable skill development. I can help review your CV and offer sessions to prepare you for real job interviews. </t>
+  </si>
+  <si>
+    <t>The UK,  London</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software development, Job Search, Motivation, Career Change, Upskill </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Data engineering best practices
+Data architecture design and implementation
+Transitioning from on-premises to cloud solutions (with focus on Databricks)
+Growing from junior to mid-level
+Growing from mid-level to senior-level
+Career development and strategic planning in data roles
+Other potential mentoring topics:
+Technology architecture &amp; strategy
+Career growth  &amp; soft skills
+Navigating the job market and building a professional brand
+Effective communication in technical teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMScreen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anastasiia Roldugina </t>
+  </si>
+  <si>
+    <t>Excited to work with motivated, curious mentees who are serious about growing in tech and open to feedback. You don’t need to have everything figured out, just a willingness to learn and try new approaches.
+I especially enjoy supporting people who are:
+        •        Early to mid-career engineers looking to build confidence and real-world skills
+        •        Transitioning into software development from another field
+        •        Preparing for technical interviews or their first (or next) engineering role
+        •        Working in startups or small teams and wanting to level up their technical and product thinking
+If you’re proactive, ask questions, and are ready to put ideas into practice between sessions, we’ll work great together.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://www.linkedin.com/in/srinivasuluparanduru/</t>
+  </si>
+  <si>
+    <t>https://dev.to/srinivasuluparanduru  &amp;   https://github.com/srinivasuluparanduru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I can arrange study group for cloud skills(AWS,Azure and GCP),Devops skills, Python &amp; GO Skills virtually </t>
+  </si>
+  <si>
+    <t xml:space="preserve">robotics, software engineering, finding the right kind of software job, resume review/technical interviews, queerness in tech, etc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm looking for a mentee who's interested in growing into new areas (research -&gt; engineering or back, physics -&gt; robotics, or anything related), or just growing from a beginner to a mid-career engineer. </t>
+  </si>
+  <si>
+    <t>1. Coding Best Practices: Delve into techniques for writing clean, maintainable, and efficient code, including code organization, naming conventions, and code documentation.
+2. Version Control Systems (VCS): Explore the fundamentals of using Git or other VCS tools effectively, including branching strategies, resolving merge conflicts, and collaborating with teams.
+3. **Software Architecture Design:** Discuss principles of software architecture, such as microservices, monolithic architectures, and design patterns, and how to make informed architectural decisions.
+4. Performance Optimization: Cover strategies for optimizing code performance, including profiling, identifying bottlenecks, and implementing optimizations without sacrificing code readability.
+5. Security Practices in Development: Review common security vulnerabilities, such as injection attacks, cross-site scripting (XSS), and how to implement secure coding practices to mitigate risks.
+6. Testing Strategies: Explore different testing methodologies, such as unit testing, integration testing, and end-to-end testing, and how to incorporate them into the development process effectively.
+7. Continuous Integration/Continuous Deployment (CI/CD): Discuss the importance of CI/CD pipelines in software development, setting up automated builds, tests, and deployments, and integrating them into the development workflow.
+8. Scalability and Performance :Examine techniques for designing scalable and high-performance systems, including load balancing, caching strategies, and horizontal/vertical scaling.
+9. Cloud Computing Technologies :such as Infrastructure as a Service (IaaS), Platform as a Service (PaaS), and Serverless computing, and how to leverage cloud services effectively in development projects.
+10. Emerging Technologies and Trends: Stay updated on the latest technologies and trends in the tech industry, such as artificial intelligence, machine learning, blockchain, and discuss their potential applications in software development projects.</t>
   </si>
 </sst>
 </file>
@@ -330,7 +1992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -343,6 +2005,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -683,7 +2351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:71" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -706,10 +2374,10 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -772,16 +2440,16 @@
         <v>25</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>26</v>
@@ -790,13 +2458,13 @@
         <v>27</v>
       </c>
       <c r="AI1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>28</v>
@@ -805,7 +2473,7 @@
         <v>29</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>32</v>
@@ -814,7 +2482,7 @@
         <v>30</v>
       </c>
       <c r="AQ1" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
@@ -845,129 +2513,121 @@
       <c r="BR1" s="3"/>
       <c r="BS1" s="3"/>
     </row>
-    <row r="2" spans="1:71" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="F2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="W2" s="4" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="AD2" s="4"/>
       <c r="AE2" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF2" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG2" s="6" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="AH2" s="7"/>
       <c r="AI2" s="4" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL2" s="7"/>
       <c r="AM2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AN2" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO2" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
       <c r="AP2" s="7"/>
       <c r="AQ2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AR2" s="7"/>
       <c r="AS2" s="7"/>
@@ -976,127 +2636,107 @@
       <c r="AV2" s="7"/>
       <c r="AW2" s="7"/>
     </row>
-    <row r="3" spans="1:71" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:71" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="T3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="V3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="W3" s="4"/>
       <c r="X3" s="4" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
       <c r="AC3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" s="4">
-        <v>4</v>
-      </c>
-      <c r="AF3" s="4"/>
-      <c r="AG3" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH3" s="7"/>
-      <c r="AI3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ3" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="AK3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL3" s="7"/>
       <c r="AM3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AN3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AO3" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
       <c r="AP3" s="7"/>
       <c r="AQ3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AR3" s="7"/>
       <c r="AS3" s="7"/>
@@ -1105,13 +2745,3721 @@
       <c r="AV3" s="7"/>
       <c r="AW3" s="7"/>
     </row>
+    <row r="4" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s">
+        <v>118</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>122</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J5" t="s">
+        <v>131</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L5" t="s">
+        <v>133</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" t="s">
+        <v>134</v>
+      </c>
+      <c r="P5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>134</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>86</v>
+      </c>
+      <c r="U5" t="s">
+        <v>67</v>
+      </c>
+      <c r="X5" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M6" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" t="s">
+        <v>149</v>
+      </c>
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" t="s">
+        <v>150</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>86</v>
+      </c>
+      <c r="U6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE6">
+        <v>2</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L7" t="s">
+        <v>165</v>
+      </c>
+      <c r="M7" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" t="s">
+        <v>84</v>
+      </c>
+      <c r="O7" t="s">
+        <v>118</v>
+      </c>
+      <c r="P7" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>83</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="U7" t="s">
+        <v>86</v>
+      </c>
+      <c r="X7" t="s">
+        <v>529</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE7">
+        <v>2</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>167</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" t="s">
+        <v>174</v>
+      </c>
+      <c r="L8" t="s">
+        <v>175</v>
+      </c>
+      <c r="M8" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>84</v>
+      </c>
+      <c r="S8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="X8" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE8">
+        <v>3</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>177</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>180</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" t="s">
+        <v>530</v>
+      </c>
+      <c r="L9" t="s">
+        <v>187</v>
+      </c>
+      <c r="M9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>189</v>
+      </c>
+      <c r="R9" t="s">
+        <v>84</v>
+      </c>
+      <c r="S9" t="s">
+        <v>66</v>
+      </c>
+      <c r="T9" t="s">
+        <v>36</v>
+      </c>
+      <c r="X9" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>190</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH9" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>193</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>194</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>195</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>200</v>
+      </c>
+      <c r="L10" t="s">
+        <v>201</v>
+      </c>
+      <c r="M10" t="s">
+        <v>81</v>
+      </c>
+      <c r="N10" t="s">
+        <v>202</v>
+      </c>
+      <c r="O10" t="s">
+        <v>189</v>
+      </c>
+      <c r="P10" t="s">
+        <v>134</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>203</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>205</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" t="s">
+        <v>531</v>
+      </c>
+      <c r="F11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" t="s">
+        <v>212</v>
+      </c>
+      <c r="L11" t="s">
+        <v>213</v>
+      </c>
+      <c r="M11" t="s">
+        <v>35</v>
+      </c>
+      <c r="N11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" t="s">
+        <v>34</v>
+      </c>
+      <c r="P11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>45</v>
+      </c>
+      <c r="R11" t="s">
+        <v>214</v>
+      </c>
+      <c r="S11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" t="s">
+        <v>86</v>
+      </c>
+      <c r="X11" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH11" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>218</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>219</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>532</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J12" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" t="s">
+        <v>226</v>
+      </c>
+      <c r="M12" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE12">
+        <v>4</v>
+      </c>
+      <c r="AF12">
+        <v>4</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>228</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>230</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>231</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" t="s">
+        <v>237</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" t="s">
+        <v>211</v>
+      </c>
+      <c r="J13" t="s">
+        <v>238</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="L13" t="s">
+        <v>240</v>
+      </c>
+      <c r="M13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N13" t="s">
+        <v>214</v>
+      </c>
+      <c r="O13" t="s">
+        <v>241</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>45</v>
+      </c>
+      <c r="R13" t="s">
+        <v>84</v>
+      </c>
+      <c r="S13" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" t="s">
+        <v>86</v>
+      </c>
+      <c r="U13" t="s">
+        <v>67</v>
+      </c>
+      <c r="V13" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13" t="s">
+        <v>87</v>
+      </c>
+      <c r="X13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>243</v>
+      </c>
+      <c r="AE13">
+        <v>4</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>244</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>245</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" t="s">
+        <v>246</v>
+      </c>
+      <c r="D14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" t="s">
+        <v>248</v>
+      </c>
+      <c r="F14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" t="s">
+        <v>250</v>
+      </c>
+      <c r="I14" t="s">
+        <v>251</v>
+      </c>
+      <c r="J14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="M14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N14" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>254</v>
+      </c>
+      <c r="R14" t="s">
+        <v>83</v>
+      </c>
+      <c r="S14" t="s">
+        <v>66</v>
+      </c>
+      <c r="T14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" t="s">
+        <v>67</v>
+      </c>
+      <c r="X14" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>255</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>256</v>
+      </c>
+      <c r="AE14">
+        <v>2</v>
+      </c>
+      <c r="AF14">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>258</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP14" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>262</v>
+      </c>
+      <c r="G15" t="s">
+        <v>162</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>263</v>
+      </c>
+      <c r="J15" t="s">
+        <v>102</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="L15" t="s">
+        <v>265</v>
+      </c>
+      <c r="M15" t="s">
+        <v>35</v>
+      </c>
+      <c r="O15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>266</v>
+      </c>
+      <c r="AE15">
+        <v>2</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>267</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>268</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>269</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>270</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" t="s">
+        <v>272</v>
+      </c>
+      <c r="C16" t="s">
+        <v>273</v>
+      </c>
+      <c r="D16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E16" t="s">
+        <v>534</v>
+      </c>
+      <c r="F16" t="s">
+        <v>275</v>
+      </c>
+      <c r="G16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" t="s">
+        <v>276</v>
+      </c>
+      <c r="L16" t="s">
+        <v>535</v>
+      </c>
+      <c r="M16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" t="s">
+        <v>189</v>
+      </c>
+      <c r="O16" t="s">
+        <v>202</v>
+      </c>
+      <c r="P16" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>241</v>
+      </c>
+      <c r="R16" t="s">
+        <v>242</v>
+      </c>
+      <c r="S16" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" t="s">
+        <v>86</v>
+      </c>
+      <c r="U16" t="s">
+        <v>66</v>
+      </c>
+      <c r="X16" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>277</v>
+      </c>
+      <c r="AE16">
+        <v>2</v>
+      </c>
+      <c r="AF16">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>278</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>279</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>280</v>
+      </c>
+      <c r="B17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" t="s">
+        <v>282</v>
+      </c>
+      <c r="E17" t="s">
+        <v>236</v>
+      </c>
+      <c r="F17" t="s">
+        <v>283</v>
+      </c>
+      <c r="G17" t="s">
+        <v>162</v>
+      </c>
+      <c r="H17" t="s">
+        <v>284</v>
+      </c>
+      <c r="I17" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" t="s">
+        <v>285</v>
+      </c>
+      <c r="L17" t="s">
+        <v>286</v>
+      </c>
+      <c r="M17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N17" t="s">
+        <v>214</v>
+      </c>
+      <c r="P17" t="s">
+        <v>241</v>
+      </c>
+      <c r="S17" t="s">
+        <v>66</v>
+      </c>
+      <c r="U17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>536</v>
+      </c>
+      <c r="AE17">
+        <v>4</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>287</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>288</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>289</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>290</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" t="s">
+        <v>293</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" t="s">
+        <v>294</v>
+      </c>
+      <c r="F18" t="s">
+        <v>295</v>
+      </c>
+      <c r="G18" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" t="s">
+        <v>211</v>
+      </c>
+      <c r="J18" t="s">
+        <v>238</v>
+      </c>
+      <c r="K18" t="s">
+        <v>296</v>
+      </c>
+      <c r="L18" t="s">
+        <v>297</v>
+      </c>
+      <c r="M18" t="s">
+        <v>35</v>
+      </c>
+      <c r="N18" t="s">
+        <v>84</v>
+      </c>
+      <c r="O18" t="s">
+        <v>214</v>
+      </c>
+      <c r="P18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>45</v>
+      </c>
+      <c r="R18" t="s">
+        <v>82</v>
+      </c>
+      <c r="S18" t="s">
+        <v>66</v>
+      </c>
+      <c r="T18" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" t="s">
+        <v>86</v>
+      </c>
+      <c r="X18" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>537</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>300</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>301</v>
+      </c>
+      <c r="B19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C19" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" t="s">
+        <v>304</v>
+      </c>
+      <c r="E19" t="s">
+        <v>305</v>
+      </c>
+      <c r="F19" t="s">
+        <v>306</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" t="s">
+        <v>130</v>
+      </c>
+      <c r="J19" t="s">
+        <v>131</v>
+      </c>
+      <c r="K19" t="s">
+        <v>307</v>
+      </c>
+      <c r="L19" t="s">
+        <v>308</v>
+      </c>
+      <c r="M19" t="s">
+        <v>81</v>
+      </c>
+      <c r="N19" t="s">
+        <v>241</v>
+      </c>
+      <c r="O19" t="s">
+        <v>188</v>
+      </c>
+      <c r="P19" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>118</v>
+      </c>
+      <c r="R19" t="s">
+        <v>134</v>
+      </c>
+      <c r="S19" t="s">
+        <v>87</v>
+      </c>
+      <c r="T19" t="s">
+        <v>85</v>
+      </c>
+      <c r="U19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V19" t="s">
+        <v>36</v>
+      </c>
+      <c r="W19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE19">
+        <v>2</v>
+      </c>
+      <c r="AF19">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>310</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>312</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>313</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" t="s">
+        <v>538</v>
+      </c>
+      <c r="D20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E20" t="s">
+        <v>539</v>
+      </c>
+      <c r="F20" t="s">
+        <v>317</v>
+      </c>
+      <c r="G20" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" t="s">
+        <v>130</v>
+      </c>
+      <c r="J20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" t="s">
+        <v>318</v>
+      </c>
+      <c r="L20" t="s">
+        <v>540</v>
+      </c>
+      <c r="M20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N20" t="s">
+        <v>242</v>
+      </c>
+      <c r="O20" t="s">
+        <v>188</v>
+      </c>
+      <c r="S20" t="s">
+        <v>87</v>
+      </c>
+      <c r="T20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>319</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>320</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>321</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>322</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>323</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>324</v>
+      </c>
+      <c r="B21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" t="s">
+        <v>324</v>
+      </c>
+      <c r="D21" t="s">
+        <v>541</v>
+      </c>
+      <c r="E21" t="s">
+        <v>326</v>
+      </c>
+      <c r="F21" t="s">
+        <v>327</v>
+      </c>
+      <c r="G21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" t="s">
+        <v>328</v>
+      </c>
+      <c r="J21" t="s">
+        <v>131</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="L21" t="s">
+        <v>330</v>
+      </c>
+      <c r="M21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N21" t="s">
+        <v>242</v>
+      </c>
+      <c r="O21" t="s">
+        <v>188</v>
+      </c>
+      <c r="P21" t="s">
+        <v>241</v>
+      </c>
+      <c r="S21" t="s">
+        <v>67</v>
+      </c>
+      <c r="T21" t="s">
+        <v>66</v>
+      </c>
+      <c r="U21" t="s">
+        <v>87</v>
+      </c>
+      <c r="V21" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC21" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>332</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>333</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>334</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>335</v>
+      </c>
+      <c r="B22" t="s">
+        <v>336</v>
+      </c>
+      <c r="C22" t="s">
+        <v>335</v>
+      </c>
+      <c r="D22" t="s">
+        <v>337</v>
+      </c>
+      <c r="E22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F22" t="s">
+        <v>339</v>
+      </c>
+      <c r="G22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" t="s">
+        <v>340</v>
+      </c>
+      <c r="I22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" t="s">
+        <v>341</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="M22" t="s">
+        <v>81</v>
+      </c>
+      <c r="N22" t="s">
+        <v>45</v>
+      </c>
+      <c r="O22" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" t="s">
+        <v>82</v>
+      </c>
+      <c r="S22" t="s">
+        <v>66</v>
+      </c>
+      <c r="T22" t="s">
+        <v>36</v>
+      </c>
+      <c r="U22" t="s">
+        <v>86</v>
+      </c>
+      <c r="X22" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE22">
+        <v>3</v>
+      </c>
+      <c r="AF22">
+        <v>2</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>344</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>346</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>347</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>313</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B23" t="s">
+        <v>349</v>
+      </c>
+      <c r="C23" t="s">
+        <v>348</v>
+      </c>
+      <c r="D23" t="s">
+        <v>350</v>
+      </c>
+      <c r="E23" t="s">
+        <v>351</v>
+      </c>
+      <c r="F23" t="s">
+        <v>352</v>
+      </c>
+      <c r="G23" t="s">
+        <v>129</v>
+      </c>
+      <c r="I23" t="s">
+        <v>353</v>
+      </c>
+      <c r="J23" t="s">
+        <v>163</v>
+      </c>
+      <c r="K23" t="s">
+        <v>354</v>
+      </c>
+      <c r="L23" t="s">
+        <v>355</v>
+      </c>
+      <c r="M23" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" t="s">
+        <v>84</v>
+      </c>
+      <c r="O23" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>202</v>
+      </c>
+      <c r="R23" t="s">
+        <v>214</v>
+      </c>
+      <c r="S23" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" t="s">
+        <v>86</v>
+      </c>
+      <c r="U23" t="s">
+        <v>67</v>
+      </c>
+      <c r="V23" t="s">
+        <v>66</v>
+      </c>
+      <c r="W23" t="s">
+        <v>85</v>
+      </c>
+      <c r="X23" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>356</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>357</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>358</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>359</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>360</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>313</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>361</v>
+      </c>
+      <c r="B24" t="s">
+        <v>362</v>
+      </c>
+      <c r="C24" t="s">
+        <v>361</v>
+      </c>
+      <c r="D24" t="s">
+        <v>159</v>
+      </c>
+      <c r="E24" t="s">
+        <v>363</v>
+      </c>
+      <c r="F24" t="s">
+        <v>364</v>
+      </c>
+      <c r="G24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" t="s">
+        <v>365</v>
+      </c>
+      <c r="I24" t="s">
+        <v>366</v>
+      </c>
+      <c r="J24" t="s">
+        <v>131</v>
+      </c>
+      <c r="K24" t="s">
+        <v>367</v>
+      </c>
+      <c r="L24" t="s">
+        <v>542</v>
+      </c>
+      <c r="M24" t="s">
+        <v>81</v>
+      </c>
+      <c r="O24" t="s">
+        <v>34</v>
+      </c>
+      <c r="P24" t="s">
+        <v>82</v>
+      </c>
+      <c r="R24" t="s">
+        <v>83</v>
+      </c>
+      <c r="S24" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>368</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>2</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>369</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>371</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>372</v>
+      </c>
+      <c r="B25" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" t="s">
+        <v>374</v>
+      </c>
+      <c r="D25" t="s">
+        <v>375</v>
+      </c>
+      <c r="E25" t="s">
+        <v>376</v>
+      </c>
+      <c r="F25" t="s">
+        <v>377</v>
+      </c>
+      <c r="G25" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" t="s">
+        <v>365</v>
+      </c>
+      <c r="I25" t="s">
+        <v>378</v>
+      </c>
+      <c r="J25" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="M25" t="s">
+        <v>81</v>
+      </c>
+      <c r="N25" t="s">
+        <v>84</v>
+      </c>
+      <c r="O25" t="s">
+        <v>134</v>
+      </c>
+      <c r="P25" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>118</v>
+      </c>
+      <c r="R25" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" t="s">
+        <v>66</v>
+      </c>
+      <c r="U25" t="s">
+        <v>67</v>
+      </c>
+      <c r="V25" t="s">
+        <v>86</v>
+      </c>
+      <c r="X25" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>381</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE25">
+        <v>2</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>382</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>383</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>384</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" t="s">
+        <v>386</v>
+      </c>
+      <c r="C26" t="s">
+        <v>385</v>
+      </c>
+      <c r="D26" t="s">
+        <v>387</v>
+      </c>
+      <c r="E26" t="s">
+        <v>388</v>
+      </c>
+      <c r="F26" t="s">
+        <v>389</v>
+      </c>
+      <c r="G26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" t="s">
+        <v>163</v>
+      </c>
+      <c r="K26" t="s">
+        <v>390</v>
+      </c>
+      <c r="L26" t="s">
+        <v>391</v>
+      </c>
+      <c r="M26" t="s">
+        <v>81</v>
+      </c>
+      <c r="N26" t="s">
+        <v>84</v>
+      </c>
+      <c r="O26" t="s">
+        <v>82</v>
+      </c>
+      <c r="P26" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>83</v>
+      </c>
+      <c r="R26" t="s">
+        <v>214</v>
+      </c>
+      <c r="S26" t="s">
+        <v>86</v>
+      </c>
+      <c r="T26" t="s">
+        <v>36</v>
+      </c>
+      <c r="U26" t="s">
+        <v>66</v>
+      </c>
+      <c r="V26" t="s">
+        <v>67</v>
+      </c>
+      <c r="W26" t="s">
+        <v>85</v>
+      </c>
+      <c r="X26" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>392</v>
+      </c>
+      <c r="AE26">
+        <v>2</v>
+      </c>
+      <c r="AF26">
+        <v>2</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>393</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>394</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>395</v>
+      </c>
+      <c r="B27" t="s">
+        <v>396</v>
+      </c>
+      <c r="C27" t="s">
+        <v>397</v>
+      </c>
+      <c r="D27" t="s">
+        <v>398</v>
+      </c>
+      <c r="E27" t="s">
+        <v>399</v>
+      </c>
+      <c r="F27" t="s">
+        <v>400</v>
+      </c>
+      <c r="G27" t="s">
+        <v>162</v>
+      </c>
+      <c r="H27" t="s">
+        <v>250</v>
+      </c>
+      <c r="I27" t="s">
+        <v>263</v>
+      </c>
+      <c r="J27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K27" t="s">
+        <v>401</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="M27" t="s">
+        <v>35</v>
+      </c>
+      <c r="N27" t="s">
+        <v>189</v>
+      </c>
+      <c r="O27" t="s">
+        <v>202</v>
+      </c>
+      <c r="P27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>134</v>
+      </c>
+      <c r="R27" t="s">
+        <v>241</v>
+      </c>
+      <c r="S27" t="s">
+        <v>66</v>
+      </c>
+      <c r="T27" t="s">
+        <v>36</v>
+      </c>
+      <c r="U27" t="s">
+        <v>67</v>
+      </c>
+      <c r="V27" t="s">
+        <v>86</v>
+      </c>
+      <c r="W27" t="s">
+        <v>85</v>
+      </c>
+      <c r="X27" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>403</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE27">
+        <v>2</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>404</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>405</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>371</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>406</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" t="s">
+        <v>44</v>
+      </c>
+      <c r="K28" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="M28" t="s">
+        <v>35</v>
+      </c>
+      <c r="N28" t="s">
+        <v>45</v>
+      </c>
+      <c r="O28" t="s">
+        <v>45</v>
+      </c>
+      <c r="P28" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>45</v>
+      </c>
+      <c r="R28" t="s">
+        <v>45</v>
+      </c>
+      <c r="S28" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" t="s">
+        <v>66</v>
+      </c>
+      <c r="U28" t="s">
+        <v>67</v>
+      </c>
+      <c r="V28" t="s">
+        <v>36</v>
+      </c>
+      <c r="W28" t="s">
+        <v>36</v>
+      </c>
+      <c r="X28" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE28">
+        <v>3</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>408</v>
+      </c>
+      <c r="B29" t="s">
+        <v>409</v>
+      </c>
+      <c r="C29" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" t="s">
+        <v>412</v>
+      </c>
+      <c r="F29" t="s">
+        <v>413</v>
+      </c>
+      <c r="G29" t="s">
+        <v>43</v>
+      </c>
+      <c r="H29" t="s">
+        <v>41</v>
+      </c>
+      <c r="I29" t="s">
+        <v>366</v>
+      </c>
+      <c r="J29" t="s">
+        <v>163</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="M29" t="s">
+        <v>81</v>
+      </c>
+      <c r="N29" t="s">
+        <v>134</v>
+      </c>
+      <c r="O29" t="s">
+        <v>134</v>
+      </c>
+      <c r="P29" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>134</v>
+      </c>
+      <c r="R29" t="s">
+        <v>189</v>
+      </c>
+      <c r="S29" t="s">
+        <v>86</v>
+      </c>
+      <c r="T29" t="s">
+        <v>36</v>
+      </c>
+      <c r="U29" t="s">
+        <v>66</v>
+      </c>
+      <c r="V29" t="s">
+        <v>36</v>
+      </c>
+      <c r="W29" t="s">
+        <v>86</v>
+      </c>
+      <c r="X29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>415</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE29">
+        <v>1</v>
+      </c>
+      <c r="AF29">
+        <v>3</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>416</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>409</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>371</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" t="s">
+        <v>418</v>
+      </c>
+      <c r="C30" t="s">
+        <v>417</v>
+      </c>
+      <c r="D30" t="s">
+        <v>419</v>
+      </c>
+      <c r="E30" t="s">
+        <v>420</v>
+      </c>
+      <c r="F30" t="s">
+        <v>421</v>
+      </c>
+      <c r="G30" t="s">
+        <v>43</v>
+      </c>
+      <c r="H30" t="s">
+        <v>422</v>
+      </c>
+      <c r="I30" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" t="s">
+        <v>131</v>
+      </c>
+      <c r="K30" t="s">
+        <v>423</v>
+      </c>
+      <c r="L30" t="s">
+        <v>424</v>
+      </c>
+      <c r="M30" t="s">
+        <v>81</v>
+      </c>
+      <c r="N30" t="s">
+        <v>214</v>
+      </c>
+      <c r="O30" t="s">
+        <v>83</v>
+      </c>
+      <c r="P30" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>189</v>
+      </c>
+      <c r="R30" t="s">
+        <v>134</v>
+      </c>
+      <c r="S30" t="s">
+        <v>36</v>
+      </c>
+      <c r="T30" t="s">
+        <v>85</v>
+      </c>
+      <c r="U30" t="s">
+        <v>67</v>
+      </c>
+      <c r="V30" t="s">
+        <v>86</v>
+      </c>
+      <c r="W30" t="s">
+        <v>87</v>
+      </c>
+      <c r="X30" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE30">
+        <v>2</v>
+      </c>
+      <c r="AF30">
+        <v>2</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>426</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>427</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>428</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>429</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>430</v>
+      </c>
+      <c r="B31" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" t="s">
+        <v>432</v>
+      </c>
+      <c r="D31" t="s">
+        <v>433</v>
+      </c>
+      <c r="E31" t="s">
+        <v>434</v>
+      </c>
+      <c r="F31" t="s">
+        <v>435</v>
+      </c>
+      <c r="G31" t="s">
+        <v>43</v>
+      </c>
+      <c r="H31" t="s">
+        <v>436</v>
+      </c>
+      <c r="I31" t="s">
+        <v>263</v>
+      </c>
+      <c r="J31" t="s">
+        <v>163</v>
+      </c>
+      <c r="K31" t="s">
+        <v>437</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="M31" t="s">
+        <v>81</v>
+      </c>
+      <c r="N31" t="s">
+        <v>241</v>
+      </c>
+      <c r="O31" t="s">
+        <v>188</v>
+      </c>
+      <c r="P31" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>242</v>
+      </c>
+      <c r="R31" t="s">
+        <v>189</v>
+      </c>
+      <c r="S31" t="s">
+        <v>66</v>
+      </c>
+      <c r="T31" t="s">
+        <v>36</v>
+      </c>
+      <c r="U31" t="s">
+        <v>86</v>
+      </c>
+      <c r="V31" t="s">
+        <v>85</v>
+      </c>
+      <c r="W31" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>439</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE31">
+        <v>4</v>
+      </c>
+      <c r="AF31">
+        <v>2</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>440</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>431</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>441</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>442</v>
+      </c>
+      <c r="B32" t="s">
+        <v>443</v>
+      </c>
+      <c r="C32" t="s">
+        <v>444</v>
+      </c>
+      <c r="D32" t="s">
+        <v>387</v>
+      </c>
+      <c r="E32" t="s">
+        <v>445</v>
+      </c>
+      <c r="F32" t="s">
+        <v>446</v>
+      </c>
+      <c r="G32" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" t="s">
+        <v>447</v>
+      </c>
+      <c r="I32" t="s">
+        <v>448</v>
+      </c>
+      <c r="J32" t="s">
+        <v>131</v>
+      </c>
+      <c r="K32" t="s">
+        <v>449</v>
+      </c>
+      <c r="L32" t="s">
+        <v>450</v>
+      </c>
+      <c r="M32" t="s">
+        <v>81</v>
+      </c>
+      <c r="N32" t="s">
+        <v>45</v>
+      </c>
+      <c r="P32" t="s">
+        <v>34</v>
+      </c>
+      <c r="S32" t="s">
+        <v>36</v>
+      </c>
+      <c r="T32" t="s">
+        <v>86</v>
+      </c>
+      <c r="X32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>451</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE32">
+        <v>5</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>452</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>453</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>454</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>455</v>
+      </c>
+      <c r="B33" t="s">
+        <v>456</v>
+      </c>
+      <c r="C33" t="s">
+        <v>455</v>
+      </c>
+      <c r="D33" t="s">
+        <v>457</v>
+      </c>
+      <c r="E33" t="s">
+        <v>248</v>
+      </c>
+      <c r="F33" t="s">
+        <v>544</v>
+      </c>
+      <c r="G33" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" t="s">
+        <v>131</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M33" t="s">
+        <v>35</v>
+      </c>
+      <c r="N33" t="s">
+        <v>84</v>
+      </c>
+      <c r="O33" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" t="s">
+        <v>82</v>
+      </c>
+      <c r="S33" t="s">
+        <v>36</v>
+      </c>
+      <c r="T33" t="s">
+        <v>67</v>
+      </c>
+      <c r="U33" t="s">
+        <v>66</v>
+      </c>
+      <c r="X33" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>460</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>461</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE33">
+        <v>5</v>
+      </c>
+      <c r="AF33">
+        <v>5</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>462</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>463</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>464</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL33" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>313</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>545</v>
+      </c>
+      <c r="B34" t="s">
+        <v>466</v>
+      </c>
+      <c r="C34" t="s">
+        <v>467</v>
+      </c>
+      <c r="D34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" t="s">
+        <v>468</v>
+      </c>
+      <c r="F34" t="s">
+        <v>469</v>
+      </c>
+      <c r="G34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" t="s">
+        <v>365</v>
+      </c>
+      <c r="I34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J34" t="s">
+        <v>131</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="L34" t="s">
+        <v>471</v>
+      </c>
+      <c r="M34" t="s">
+        <v>81</v>
+      </c>
+      <c r="N34" t="s">
+        <v>34</v>
+      </c>
+      <c r="S34" t="s">
+        <v>36</v>
+      </c>
+      <c r="T34" t="s">
+        <v>86</v>
+      </c>
+      <c r="U34" t="s">
+        <v>67</v>
+      </c>
+      <c r="V34" t="s">
+        <v>87</v>
+      </c>
+      <c r="X34" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC34" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE34">
+        <v>4</v>
+      </c>
+      <c r="AF34">
+        <v>2</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>472</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>473</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>474</v>
+      </c>
+      <c r="B35" t="s">
+        <v>475</v>
+      </c>
+      <c r="C35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E35" t="s">
+        <v>477</v>
+      </c>
+      <c r="F35" t="s">
+        <v>478</v>
+      </c>
+      <c r="G35" t="s">
+        <v>43</v>
+      </c>
+      <c r="H35" t="s">
+        <v>479</v>
+      </c>
+      <c r="I35" t="s">
+        <v>480</v>
+      </c>
+      <c r="J35" t="s">
+        <v>78</v>
+      </c>
+      <c r="K35" t="s">
+        <v>481</v>
+      </c>
+      <c r="L35" t="s">
+        <v>482</v>
+      </c>
+      <c r="M35" t="s">
+        <v>35</v>
+      </c>
+      <c r="N35" t="s">
+        <v>83</v>
+      </c>
+      <c r="O35" t="s">
+        <v>84</v>
+      </c>
+      <c r="P35" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>134</v>
+      </c>
+      <c r="R35" t="s">
+        <v>214</v>
+      </c>
+      <c r="S35" t="s">
+        <v>85</v>
+      </c>
+      <c r="T35" t="s">
+        <v>86</v>
+      </c>
+      <c r="U35" t="s">
+        <v>36</v>
+      </c>
+      <c r="V35" t="s">
+        <v>67</v>
+      </c>
+      <c r="W35" t="s">
+        <v>66</v>
+      </c>
+      <c r="X35" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>255</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>483</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE35">
+        <v>3</v>
+      </c>
+      <c r="AF35">
+        <v>6</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>547</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>548</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>484</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>549</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>122</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>313</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>485</v>
+      </c>
+      <c r="AQ35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>486</v>
+      </c>
+      <c r="B36" t="s">
+        <v>487</v>
+      </c>
+      <c r="C36" t="s">
+        <v>486</v>
+      </c>
+      <c r="D36" t="s">
+        <v>488</v>
+      </c>
+      <c r="E36" t="s">
+        <v>489</v>
+      </c>
+      <c r="F36" t="s">
+        <v>490</v>
+      </c>
+      <c r="G36" t="s">
+        <v>43</v>
+      </c>
+      <c r="H36" t="s">
+        <v>365</v>
+      </c>
+      <c r="I36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36" t="s">
+        <v>102</v>
+      </c>
+      <c r="K36" t="s">
+        <v>491</v>
+      </c>
+      <c r="L36" t="s">
+        <v>550</v>
+      </c>
+      <c r="M36" t="s">
+        <v>35</v>
+      </c>
+      <c r="N36" t="s">
+        <v>34</v>
+      </c>
+      <c r="O36" t="s">
+        <v>84</v>
+      </c>
+      <c r="P36" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>202</v>
+      </c>
+      <c r="R36" t="s">
+        <v>83</v>
+      </c>
+      <c r="S36" t="s">
+        <v>36</v>
+      </c>
+      <c r="X36" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>492</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE36">
+        <v>2</v>
+      </c>
+      <c r="AF36">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>493</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>487</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>494</v>
+      </c>
+      <c r="B37" t="s">
+        <v>495</v>
+      </c>
+      <c r="C37" t="s">
+        <v>496</v>
+      </c>
+      <c r="D37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" t="s">
+        <v>497</v>
+      </c>
+      <c r="F37" t="s">
+        <v>498</v>
+      </c>
+      <c r="G37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H37" t="s">
+        <v>499</v>
+      </c>
+      <c r="I37" t="s">
+        <v>500</v>
+      </c>
+      <c r="J37" t="s">
+        <v>44</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="M37" t="s">
+        <v>35</v>
+      </c>
+      <c r="N37" t="s">
+        <v>83</v>
+      </c>
+      <c r="O37" t="s">
+        <v>503</v>
+      </c>
+      <c r="P37" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>504</v>
+      </c>
+      <c r="S37" t="s">
+        <v>67</v>
+      </c>
+      <c r="T37" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC37" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE37">
+        <v>1</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>506</v>
+      </c>
+      <c r="AH37" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>508</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>509</v>
+      </c>
+      <c r="AO37" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP37" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>511</v>
+      </c>
+      <c r="B38" t="s">
+        <v>512</v>
+      </c>
+      <c r="C38" t="s">
+        <v>511</v>
+      </c>
+      <c r="D38" t="s">
+        <v>513</v>
+      </c>
+      <c r="E38" t="s">
+        <v>248</v>
+      </c>
+      <c r="F38" t="s">
+        <v>490</v>
+      </c>
+      <c r="G38" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" t="s">
+        <v>365</v>
+      </c>
+      <c r="I38" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" t="s">
+        <v>131</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="M38" t="s">
+        <v>81</v>
+      </c>
+      <c r="O38" t="s">
+        <v>84</v>
+      </c>
+      <c r="P38" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>82</v>
+      </c>
+      <c r="R38" t="s">
+        <v>134</v>
+      </c>
+      <c r="S38" t="s">
+        <v>36</v>
+      </c>
+      <c r="X38" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>551</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE38">
+        <v>1</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>516</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>517</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>518</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>519</v>
+      </c>
+      <c r="B39" t="s">
+        <v>520</v>
+      </c>
+      <c r="C39" t="s">
+        <v>519</v>
+      </c>
+      <c r="D39" t="s">
+        <v>521</v>
+      </c>
+      <c r="E39" t="s">
+        <v>294</v>
+      </c>
+      <c r="F39" t="s">
+        <v>522</v>
+      </c>
+      <c r="G39" t="s">
+        <v>523</v>
+      </c>
+      <c r="I39" t="s">
+        <v>353</v>
+      </c>
+      <c r="J39" t="s">
+        <v>131</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="M39" t="s">
+        <v>81</v>
+      </c>
+      <c r="N39" t="s">
+        <v>84</v>
+      </c>
+      <c r="O39" t="s">
+        <v>45</v>
+      </c>
+      <c r="P39" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>83</v>
+      </c>
+      <c r="R39" t="s">
+        <v>254</v>
+      </c>
+      <c r="S39" t="s">
+        <v>36</v>
+      </c>
+      <c r="T39" t="s">
+        <v>87</v>
+      </c>
+      <c r="U39" t="s">
+        <v>67</v>
+      </c>
+      <c r="V39" t="s">
+        <v>66</v>
+      </c>
+      <c r="W39" t="s">
+        <v>86</v>
+      </c>
+      <c r="X39" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>529</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>525</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>3</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>526</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>527</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL39" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ39" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="AG2" r:id="rId1" xr:uid="{936BE823-E5D2-034A-A93C-C51AF78D1939}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{D07A4C28-1384-6145-B49B-4EA7D34CF389}"/>
-    <hyperlink ref="AG3" r:id="rId3" xr:uid="{EFA0AFF0-0687-3F4D-9B36-BA8A8FCA4A21}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{D535B5EB-6D8B-6442-8AD9-A0B1C632CE98}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1123,10 +6471,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1134,15 +6482,15 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
